--- a/backtest_v3.xlsx
+++ b/backtest_v3.xlsx
@@ -3606,7 +3606,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -4748,37 +4748,37 @@
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="22" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>South Korea vs Czechia</t>
         </is>
       </c>
-      <c r="B39" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>91.2%</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F39" s="23" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G39" s="23" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="F42" s="23" t="inlineStr">
@@ -4896,37 +4896,37 @@
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="22" t="inlineStr">
         <is>
           <t>South Korea vs Czechia</t>
         </is>
       </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>Goals O/U 3.5</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 3.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
         <is>
           <t>Under 3.5</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="23" t="inlineStr">
         <is>
           <t>75.2%</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="E43" s="23" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G43" s="23" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
@@ -6050,37 +6050,37 @@
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="22" t="inlineStr">
+      <c r="A76" s="18" t="inlineStr">
         <is>
           <t>Canada vs Bosnia and Herzegovina</t>
         </is>
       </c>
-      <c r="B76" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C76" s="23" t="inlineStr">
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D76" s="23" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>93.0%</t>
         </is>
       </c>
-      <c r="E76" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="23" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G76" s="23" t="inlineStr">
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -6124,37 +6124,37 @@
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="18" t="inlineStr">
+      <c r="A78" s="22" t="inlineStr">
         <is>
           <t>Canada vs Bosnia and Herzegovina</t>
         </is>
       </c>
-      <c r="B78" s="18" t="inlineStr">
-        <is>
-          <t>Draw No Bet Canada</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>Victorie</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>Draw No Bet Canada *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C78" s="23" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="D78" s="23" t="inlineStr">
         <is>
           <t>84.7%</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="E78" s="23" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F78" s="23" t="inlineStr">
         <is>
           <t>dnb</t>
         </is>
       </c>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="G78" s="23" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -6235,37 +6235,37 @@
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="17" t="inlineStr">
+      <c r="A81" s="22" t="inlineStr">
         <is>
           <t>Canada vs Bosnia and Herzegovina</t>
         </is>
       </c>
-      <c r="B81" s="17" t="inlineStr">
-        <is>
-          <t>Goals O/U 1.5</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 1.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C81" s="23" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D81" s="23" t="inlineStr">
         <is>
           <t>76.9%</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="E81" s="23" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G81" s="3" t="inlineStr">
+      <c r="G81" s="23" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -6531,37 +6531,37 @@
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
-      <c r="A89" s="22" t="inlineStr">
+      <c r="A89" s="17" t="inlineStr">
         <is>
           <t>Canada vs Bosnia and Herzegovina</t>
         </is>
       </c>
-      <c r="B89" s="22" t="inlineStr">
-        <is>
-          <t>1X2 Result *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C89" s="23" t="inlineStr">
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>1X2 Result</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>1 (Canada)</t>
         </is>
       </c>
-      <c r="D89" s="23" t="inlineStr">
+      <c r="D89" s="15" t="inlineStr">
         <is>
           <t>60.8%</t>
         </is>
       </c>
-      <c r="E89" s="23" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>1.80</t>
         </is>
       </c>
-      <c r="F89" s="23" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="G89" s="23" t="inlineStr">
+      <c r="G89" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
@@ -7426,37 +7426,37 @@
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
-      <c r="A115" s="22" t="inlineStr">
+      <c r="A115" s="17" t="inlineStr">
         <is>
           <t>United States vs Paraguay</t>
         </is>
       </c>
-      <c r="B115" s="22" t="inlineStr">
-        <is>
-          <t>Fouls O/U 20.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C115" s="23" t="inlineStr">
+      <c r="B115" s="17" t="inlineStr">
+        <is>
+          <t>Fouls O/U 20.5</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
         <is>
           <t>Over 20.5</t>
         </is>
       </c>
-      <c r="D115" s="23" t="inlineStr">
+      <c r="D115" s="4" t="inlineStr">
         <is>
           <t>75.3%</t>
         </is>
       </c>
-      <c r="E115" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F115" s="23" t="inlineStr">
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
         <is>
           <t>fouls</t>
         </is>
       </c>
-      <c r="G115" s="23" t="inlineStr">
+      <c r="G115" s="3" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -7611,37 +7611,37 @@
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="18" t="inlineStr">
+      <c r="A120" s="22" t="inlineStr">
         <is>
           <t>United States vs Paraguay</t>
         </is>
       </c>
-      <c r="B120" s="18" t="inlineStr">
-        <is>
-          <t>Double Chance X2</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
+      <c r="B120" s="22" t="inlineStr">
+        <is>
+          <t>Double Chance X2 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C120" s="23" t="inlineStr">
         <is>
           <t>X2</t>
         </is>
       </c>
-      <c r="D120" s="15" t="inlineStr">
+      <c r="D120" s="23" t="inlineStr">
         <is>
           <t>67.8%</t>
         </is>
       </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr">
+      <c r="E120" s="23" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="F120" s="23" t="inlineStr">
         <is>
           <t>dc</t>
         </is>
       </c>
-      <c r="G120" s="5" t="inlineStr">
+      <c r="G120" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
@@ -8950,37 +8950,37 @@
       </c>
     </row>
     <row r="158" ht="15" customHeight="1">
-      <c r="A158" s="18" t="inlineStr">
+      <c r="A158" s="22" t="inlineStr">
         <is>
           <t>Qatar vs Switzerland</t>
         </is>
       </c>
-      <c r="B158" s="18" t="inlineStr">
-        <is>
-          <t>Goals O/U 3.5</t>
-        </is>
-      </c>
-      <c r="C158" s="5" t="inlineStr">
+      <c r="B158" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 3.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C158" s="23" t="inlineStr">
         <is>
           <t>Under 3.5</t>
         </is>
       </c>
-      <c r="D158" s="15" t="inlineStr">
+      <c r="D158" s="23" t="inlineStr">
         <is>
           <t>71.4%</t>
         </is>
       </c>
-      <c r="E158" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F158" s="5" t="inlineStr">
+      <c r="E158" s="23" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="F158" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G158" s="5" t="inlineStr">
+      <c r="G158" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -9061,37 +9061,37 @@
       </c>
     </row>
     <row r="161" ht="15" customHeight="1">
-      <c r="A161" s="22" t="inlineStr">
+      <c r="A161" s="17" t="inlineStr">
         <is>
           <t>Qatar vs Switzerland</t>
         </is>
       </c>
-      <c r="B161" s="22" t="inlineStr">
-        <is>
-          <t>GG (Both Teams Score) *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C161" s="23" t="inlineStr">
+      <c r="B161" s="17" t="inlineStr">
+        <is>
+          <t>GG (Both Teams Score)</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="D161" s="23" t="inlineStr">
+      <c r="D161" s="11" t="inlineStr">
         <is>
           <t>58.2%</t>
         </is>
       </c>
-      <c r="E161" s="23" t="inlineStr">
+      <c r="E161" s="3" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="F161" s="23" t="inlineStr">
+      <c r="F161" s="3" t="inlineStr">
         <is>
           <t>gg</t>
         </is>
       </c>
-      <c r="G161" s="23" t="inlineStr">
+      <c r="G161" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -9771,37 +9771,37 @@
       </c>
     </row>
     <row r="182" ht="15" customHeight="1">
-      <c r="A182" s="22" t="inlineStr">
+      <c r="A182" s="18" t="inlineStr">
         <is>
           <t>Brazil vs Morocco</t>
         </is>
       </c>
-      <c r="B182" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C182" s="23" t="inlineStr">
+      <c r="B182" s="18" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D182" s="23" t="inlineStr">
+      <c r="D182" s="4" t="inlineStr">
         <is>
           <t>91.8%</t>
         </is>
       </c>
-      <c r="E182" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F182" s="23" t="inlineStr">
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F182" s="5" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G182" s="23" t="inlineStr">
+      <c r="G182" s="5" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
@@ -10030,37 +10030,37 @@
       </c>
     </row>
     <row r="189" ht="15" customHeight="1">
-      <c r="A189" s="17" t="inlineStr">
+      <c r="A189" s="22" t="inlineStr">
         <is>
           <t>Brazil vs Morocco</t>
         </is>
       </c>
-      <c r="B189" s="17" t="inlineStr">
-        <is>
-          <t>Goals O/U 1.5</t>
-        </is>
-      </c>
-      <c r="C189" s="3" t="inlineStr">
+      <c r="B189" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 1.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C189" s="23" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="D189" s="15" t="inlineStr">
+      <c r="D189" s="23" t="inlineStr">
         <is>
           <t>73.8%</t>
         </is>
       </c>
-      <c r="E189" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F189" s="3" t="inlineStr">
+      <c r="E189" s="23" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F189" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G189" s="3" t="inlineStr">
+      <c r="G189" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D206" s="12" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F206" s="5" t="inlineStr">
@@ -11036,37 +11036,37 @@
       </c>
     </row>
     <row r="218" ht="15" customHeight="1">
-      <c r="A218" s="22" t="inlineStr">
+      <c r="A218" s="18" t="inlineStr">
         <is>
           <t>Haiti vs Scotland</t>
         </is>
       </c>
-      <c r="B218" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C218" s="23" t="inlineStr">
+      <c r="B218" s="18" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D218" s="23" t="inlineStr">
+      <c r="D218" s="4" t="inlineStr">
         <is>
           <t>92.2%</t>
         </is>
       </c>
-      <c r="E218" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F218" s="23" t="inlineStr">
+      <c r="E218" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F218" s="5" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G218" s="23" t="inlineStr">
+      <c r="G218" s="5" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -11110,37 +11110,37 @@
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
-      <c r="A220" s="18" t="inlineStr">
+      <c r="A220" s="22" t="inlineStr">
         <is>
           <t>Haiti vs Scotland</t>
         </is>
       </c>
-      <c r="B220" s="18" t="inlineStr">
-        <is>
-          <t>Double Chance X2</t>
-        </is>
-      </c>
-      <c r="C220" s="5" t="inlineStr">
+      <c r="B220" s="22" t="inlineStr">
+        <is>
+          <t>Double Chance X2 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C220" s="23" t="inlineStr">
         <is>
           <t>X2</t>
         </is>
       </c>
-      <c r="D220" s="4" t="inlineStr">
+      <c r="D220" s="23" t="inlineStr">
         <is>
           <t>81.1%</t>
         </is>
       </c>
-      <c r="E220" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F220" s="5" t="inlineStr">
+      <c r="E220" s="23" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="F220" s="23" t="inlineStr">
         <is>
           <t>dc</t>
         </is>
       </c>
-      <c r="G220" s="5" t="inlineStr">
+      <c r="G220" s="23" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
@@ -11295,37 +11295,37 @@
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
-      <c r="A225" s="17" t="inlineStr">
+      <c r="A225" s="22" t="inlineStr">
         <is>
           <t>Haiti vs Scotland</t>
         </is>
       </c>
-      <c r="B225" s="17" t="inlineStr">
-        <is>
-          <t>Goals O/U 1.5</t>
-        </is>
-      </c>
-      <c r="C225" s="3" t="inlineStr">
+      <c r="B225" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 1.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C225" s="23" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="D225" s="4" t="inlineStr">
+      <c r="D225" s="23" t="inlineStr">
         <is>
           <t>75.0%</t>
         </is>
       </c>
-      <c r="E225" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F225" s="3" t="inlineStr">
+      <c r="E225" s="23" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="F225" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G225" s="3" t="inlineStr">
+      <c r="G225" s="23" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="E226" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
@@ -11517,37 +11517,37 @@
       </c>
     </row>
     <row r="231" ht="15" customHeight="1">
-      <c r="A231" s="22" t="inlineStr">
+      <c r="A231" s="17" t="inlineStr">
         <is>
           <t>Haiti vs Scotland</t>
         </is>
       </c>
-      <c r="B231" s="22" t="inlineStr">
-        <is>
-          <t>1X2 Result *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C231" s="23" t="inlineStr">
+      <c r="B231" s="17" t="inlineStr">
+        <is>
+          <t>1X2 Result</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
         <is>
           <t>2 (Scotland)</t>
         </is>
       </c>
-      <c r="D231" s="23" t="inlineStr">
+      <c r="D231" s="11" t="inlineStr">
         <is>
           <t>58.2%</t>
         </is>
       </c>
-      <c r="E231" s="23" t="inlineStr">
+      <c r="E231" s="3" t="inlineStr">
         <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="F231" s="23" t="inlineStr">
+      <c r="F231" s="3" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="G231" s="23" t="inlineStr">
+      <c r="G231" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -11687,7 +11687,7 @@
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D240" s="12" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
@@ -12227,37 +12227,37 @@
       </c>
     </row>
     <row r="252" ht="15" customHeight="1">
-      <c r="A252" s="22" t="inlineStr">
+      <c r="A252" s="18" t="inlineStr">
         <is>
           <t>Australia vs Turkey</t>
         </is>
       </c>
-      <c r="B252" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C252" s="23" t="inlineStr">
+      <c r="B252" s="18" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C252" s="5" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D252" s="23" t="inlineStr">
+      <c r="D252" s="4" t="inlineStr">
         <is>
           <t>92.1%</t>
         </is>
       </c>
-      <c r="E252" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F252" s="23" t="inlineStr">
+      <c r="E252" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F252" s="5" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G252" s="23" t="inlineStr">
+      <c r="G252" s="5" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -12286,7 +12286,7 @@
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
@@ -12486,37 +12486,37 @@
       </c>
     </row>
     <row r="259" ht="15" customHeight="1">
-      <c r="A259" s="17" t="inlineStr">
+      <c r="A259" s="22" t="inlineStr">
         <is>
           <t>Australia vs Turkey</t>
         </is>
       </c>
-      <c r="B259" s="17" t="inlineStr">
-        <is>
-          <t>Goals O/U 1.5</t>
-        </is>
-      </c>
-      <c r="C259" s="3" t="inlineStr">
+      <c r="B259" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 1.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C259" s="23" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="D259" s="15" t="inlineStr">
+      <c r="D259" s="23" t="inlineStr">
         <is>
           <t>74.7%</t>
         </is>
       </c>
-      <c r="E259" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F259" s="3" t="inlineStr">
+      <c r="E259" s="23" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F259" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G259" s="3" t="inlineStr">
+      <c r="G259" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -12545,7 +12545,7 @@
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D275" s="12" t="inlineStr">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -13455,37 +13455,37 @@
       </c>
     </row>
     <row r="287" ht="15" customHeight="1">
-      <c r="A287" s="17" t="inlineStr">
+      <c r="A287" s="22" t="inlineStr">
         <is>
           <t>Germany vs Curaçao</t>
         </is>
       </c>
-      <c r="B287" s="17" t="inlineStr">
-        <is>
-          <t>Double Chance 1X</t>
-        </is>
-      </c>
-      <c r="C287" s="3" t="inlineStr">
+      <c r="B287" s="22" t="inlineStr">
+        <is>
+          <t>Double Chance 1X *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C287" s="23" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="D287" s="4" t="inlineStr">
+      <c r="D287" s="23" t="inlineStr">
         <is>
           <t>94.7%</t>
         </is>
       </c>
-      <c r="E287" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F287" s="3" t="inlineStr">
+      <c r="E287" s="23" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="F287" s="23" t="inlineStr">
         <is>
           <t>dc</t>
         </is>
       </c>
-      <c r="G287" s="3" t="inlineStr">
+      <c r="G287" s="23" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -13504,7 +13504,7 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
@@ -13714,37 +13714,37 @@
       </c>
     </row>
     <row r="294" ht="15" customHeight="1">
-      <c r="A294" s="22" t="inlineStr">
+      <c r="A294" s="18" t="inlineStr">
         <is>
           <t>Germany vs Curaçao</t>
         </is>
       </c>
-      <c r="B294" s="22" t="inlineStr">
-        <is>
-          <t>1X2 Result *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C294" s="23" t="inlineStr">
+      <c r="B294" s="18" t="inlineStr">
+        <is>
+          <t>1X2 Result</t>
+        </is>
+      </c>
+      <c r="C294" s="5" t="inlineStr">
         <is>
           <t>1 (Germany)</t>
         </is>
       </c>
-      <c r="D294" s="23" t="inlineStr">
+      <c r="D294" s="4" t="inlineStr">
         <is>
           <t>85.0%</t>
         </is>
       </c>
-      <c r="E294" s="23" t="inlineStr">
+      <c r="E294" s="5" t="inlineStr">
         <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="F294" s="23" t="inlineStr">
+      <c r="F294" s="5" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="G294" s="23" t="inlineStr">
+      <c r="G294" s="5" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -13810,7 +13810,7 @@
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="F296" s="5" t="inlineStr">
@@ -13825,37 +13825,37 @@
       </c>
     </row>
     <row r="297" ht="15" customHeight="1">
-      <c r="A297" s="17" t="inlineStr">
+      <c r="A297" s="22" t="inlineStr">
         <is>
           <t>Germany vs Curaçao</t>
         </is>
       </c>
-      <c r="B297" s="17" t="inlineStr">
-        <is>
-          <t>Goals O/U 3.5</t>
-        </is>
-      </c>
-      <c r="C297" s="3" t="inlineStr">
+      <c r="B297" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 3.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C297" s="23" t="inlineStr">
         <is>
           <t>Under 3.5</t>
         </is>
       </c>
-      <c r="D297" s="15" t="inlineStr">
+      <c r="D297" s="23" t="inlineStr">
         <is>
           <t>72.5%</t>
         </is>
       </c>
-      <c r="E297" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F297" s="3" t="inlineStr">
+      <c r="E297" s="23" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="F297" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G297" s="3" t="inlineStr">
+      <c r="G297" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -14010,37 +14010,37 @@
       </c>
     </row>
     <row r="302" ht="15" customHeight="1">
-      <c r="A302" s="22" t="inlineStr">
+      <c r="A302" s="18" t="inlineStr">
         <is>
           <t>Germany vs Curaçao</t>
         </is>
       </c>
-      <c r="B302" s="22" t="inlineStr">
-        <is>
-          <t>GG (Both Teams Score) *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C302" s="23" t="inlineStr">
+      <c r="B302" s="18" t="inlineStr">
+        <is>
+          <t>GG (Both Teams Score)</t>
+        </is>
+      </c>
+      <c r="C302" s="5" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="D302" s="23" t="inlineStr">
+      <c r="D302" s="11" t="inlineStr">
         <is>
           <t>56.3%</t>
         </is>
       </c>
-      <c r="E302" s="23" t="inlineStr">
+      <c r="E302" s="5" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="F302" s="23" t="inlineStr">
+      <c r="F302" s="5" t="inlineStr">
         <is>
           <t>gg</t>
         </is>
       </c>
-      <c r="G302" s="23" t="inlineStr">
+      <c r="G302" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="E304" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="F304" s="5" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="E308" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="F308" s="5" t="inlineStr">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D317" s="12" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="E317" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="F317" s="3" t="inlineStr">
@@ -14646,37 +14646,37 @@
       </c>
     </row>
     <row r="321" ht="15" customHeight="1">
-      <c r="A321" s="22" t="inlineStr">
+      <c r="A321" s="17" t="inlineStr">
         <is>
           <t>Netherlands vs Japan</t>
         </is>
       </c>
-      <c r="B321" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C321" s="23" t="inlineStr">
+      <c r="B321" s="17" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D321" s="23" t="inlineStr">
+      <c r="D321" s="4" t="inlineStr">
         <is>
           <t>91.6%</t>
         </is>
       </c>
-      <c r="E321" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F321" s="23" t="inlineStr">
+      <c r="E321" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F321" s="3" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G321" s="23" t="inlineStr">
+      <c r="G321" s="3" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -14757,111 +14757,111 @@
       </c>
     </row>
     <row r="324" ht="15" customHeight="1">
-      <c r="A324" s="22" t="inlineStr">
+      <c r="A324" s="18" t="inlineStr">
         <is>
           <t>Netherlands vs Japan</t>
         </is>
       </c>
-      <c r="B324" s="22" t="inlineStr">
-        <is>
-          <t>Scorer Memphis Depay (Netherla) *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C324" s="23" t="inlineStr">
+      <c r="B324" s="18" t="inlineStr">
+        <is>
+          <t>Scorer Memphis Depay (Netherla)</t>
+        </is>
+      </c>
+      <c r="C324" s="5" t="inlineStr">
         <is>
           <t>To Score</t>
         </is>
       </c>
-      <c r="D324" s="23" t="inlineStr">
+      <c r="D324" s="4" t="inlineStr">
         <is>
           <t>76.9%</t>
         </is>
       </c>
-      <c r="E324" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F324" s="23" t="inlineStr">
+      <c r="E324" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F324" s="5" t="inlineStr">
         <is>
           <t>scorers</t>
         </is>
       </c>
-      <c r="G324" s="23" t="inlineStr">
+      <c r="G324" s="5" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
-      <c r="A325" s="17" t="inlineStr">
+      <c r="A325" s="22" t="inlineStr">
         <is>
           <t>Netherlands vs Japan</t>
         </is>
       </c>
-      <c r="B325" s="17" t="inlineStr">
-        <is>
-          <t>Double Chance X2</t>
-        </is>
-      </c>
-      <c r="C325" s="3" t="inlineStr">
+      <c r="B325" s="22" t="inlineStr">
+        <is>
+          <t>Double Chance X2 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C325" s="23" t="inlineStr">
         <is>
           <t>X2</t>
         </is>
       </c>
-      <c r="D325" s="15" t="inlineStr">
+      <c r="D325" s="23" t="inlineStr">
         <is>
           <t>74.1%</t>
         </is>
       </c>
-      <c r="E325" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F325" s="3" t="inlineStr">
+      <c r="E325" s="23" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="F325" s="23" t="inlineStr">
         <is>
           <t>dc</t>
         </is>
       </c>
-      <c r="G325" s="3" t="inlineStr">
+      <c r="G325" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="326" ht="15" customHeight="1">
-      <c r="A326" s="18" t="inlineStr">
+      <c r="A326" s="22" t="inlineStr">
         <is>
           <t>Netherlands vs Japan</t>
         </is>
       </c>
-      <c r="B326" s="18" t="inlineStr">
-        <is>
-          <t>Goals O/U 3.5</t>
-        </is>
-      </c>
-      <c r="C326" s="5" t="inlineStr">
+      <c r="B326" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 3.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C326" s="23" t="inlineStr">
         <is>
           <t>Under 3.5</t>
         </is>
       </c>
-      <c r="D326" s="15" t="inlineStr">
+      <c r="D326" s="23" t="inlineStr">
         <is>
           <t>74.1%</t>
         </is>
       </c>
-      <c r="E326" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F326" s="5" t="inlineStr">
+      <c r="E326" s="23" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F326" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G326" s="5" t="inlineStr">
+      <c r="G326" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="E327" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F327" s="3" t="inlineStr">
@@ -15075,7 +15075,7 @@
       </c>
       <c r="E332" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F332" s="5" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="E334" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F334" s="5" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="C335" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D335" s="11" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="E337" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="F337" s="3" t="inlineStr">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="C341" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D341" s="12" t="inlineStr">
@@ -15985,37 +15985,37 @@
       </c>
     </row>
     <row r="359" ht="15" customHeight="1">
-      <c r="A359" s="22" t="inlineStr">
+      <c r="A359" s="17" t="inlineStr">
         <is>
           <t>Ivory Coast vs Ecuador</t>
         </is>
       </c>
-      <c r="B359" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C359" s="23" t="inlineStr">
+      <c r="B359" s="17" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C359" s="3" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D359" s="23" t="inlineStr">
+      <c r="D359" s="4" t="inlineStr">
         <is>
           <t>91.6%</t>
         </is>
       </c>
-      <c r="E359" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F359" s="23" t="inlineStr">
+      <c r="E359" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F359" s="3" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G359" s="23" t="inlineStr">
+      <c r="G359" s="3" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -16059,37 +16059,37 @@
       </c>
     </row>
     <row r="361" ht="15" customHeight="1">
-      <c r="A361" s="22" t="inlineStr">
+      <c r="A361" s="17" t="inlineStr">
         <is>
           <t>Ivory Coast vs Ecuador</t>
         </is>
       </c>
-      <c r="B361" s="22" t="inlineStr">
-        <is>
-          <t>Fouls O/U 24.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C361" s="23" t="inlineStr">
+      <c r="B361" s="17" t="inlineStr">
+        <is>
+          <t>Fouls O/U 24.5</t>
+        </is>
+      </c>
+      <c r="C361" s="3" t="inlineStr">
         <is>
           <t>Under 24.5</t>
         </is>
       </c>
-      <c r="D361" s="23" t="inlineStr">
+      <c r="D361" s="4" t="inlineStr">
         <is>
           <t>78.1%</t>
         </is>
       </c>
-      <c r="E361" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F361" s="23" t="inlineStr">
+      <c r="E361" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F361" s="3" t="inlineStr">
         <is>
           <t>fouls</t>
         </is>
       </c>
-      <c r="G361" s="23" t="inlineStr">
+      <c r="G361" s="3" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="E362" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="F362" s="5" t="inlineStr">
@@ -16155,7 +16155,7 @@
       </c>
       <c r="E363" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F363" s="3" t="inlineStr">
@@ -16207,37 +16207,37 @@
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
-      <c r="A365" s="17" t="inlineStr">
+      <c r="A365" s="22" t="inlineStr">
         <is>
           <t>Ivory Coast vs Ecuador</t>
         </is>
       </c>
-      <c r="B365" s="17" t="inlineStr">
-        <is>
-          <t>Goals O/U 1.5</t>
-        </is>
-      </c>
-      <c r="C365" s="3" t="inlineStr">
+      <c r="B365" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 1.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C365" s="23" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="D365" s="15" t="inlineStr">
+      <c r="D365" s="23" t="inlineStr">
         <is>
           <t>73.4%</t>
         </is>
       </c>
-      <c r="E365" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F365" s="3" t="inlineStr">
+      <c r="E365" s="23" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="F365" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G365" s="3" t="inlineStr">
+      <c r="G365" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -16355,37 +16355,37 @@
       </c>
     </row>
     <row r="369" ht="15" customHeight="1">
-      <c r="A369" s="17" t="inlineStr">
+      <c r="A369" s="22" t="inlineStr">
         <is>
           <t>Ivory Coast vs Ecuador</t>
         </is>
       </c>
-      <c r="B369" s="17" t="inlineStr">
-        <is>
-          <t>Double Chance 1X</t>
-        </is>
-      </c>
-      <c r="C369" s="3" t="inlineStr">
+      <c r="B369" s="22" t="inlineStr">
+        <is>
+          <t>Double Chance 1X *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C369" s="23" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="D369" s="15" t="inlineStr">
+      <c r="D369" s="23" t="inlineStr">
         <is>
           <t>66.1%</t>
         </is>
       </c>
-      <c r="E369" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F369" s="3" t="inlineStr">
+      <c r="E369" s="23" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="F369" s="23" t="inlineStr">
         <is>
           <t>dc</t>
         </is>
       </c>
-      <c r="G369" s="3" t="inlineStr">
+      <c r="G369" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="E373" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="F373" s="3" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="C374" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D374" s="11" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="E378" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F378" s="5" t="inlineStr">
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C379" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D379" s="11" t="inlineStr">
@@ -17250,37 +17250,37 @@
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
-      <c r="A395" s="22" t="inlineStr">
+      <c r="A395" s="17" t="inlineStr">
         <is>
           <t>Sweden vs Tunisia</t>
         </is>
       </c>
-      <c r="B395" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C395" s="23" t="inlineStr">
+      <c r="B395" s="17" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C395" s="3" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D395" s="23" t="inlineStr">
+      <c r="D395" s="4" t="inlineStr">
         <is>
           <t>91.0%</t>
         </is>
       </c>
-      <c r="E395" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F395" s="23" t="inlineStr">
+      <c r="E395" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F395" s="3" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G395" s="23" t="inlineStr">
+      <c r="G395" s="3" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -17309,7 +17309,7 @@
       </c>
       <c r="E396" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="F396" s="5" t="inlineStr">
@@ -17383,7 +17383,7 @@
       </c>
       <c r="E398" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F398" s="5" t="inlineStr">
@@ -17410,7 +17410,7 @@
       </c>
       <c r="C399" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D399" s="4" t="inlineStr">
@@ -17457,7 +17457,7 @@
       </c>
       <c r="E400" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F400" s="5" t="inlineStr">
@@ -17509,37 +17509,37 @@
       </c>
     </row>
     <row r="402" ht="15" customHeight="1">
-      <c r="A402" s="18" t="inlineStr">
+      <c r="A402" s="22" t="inlineStr">
         <is>
           <t>Sweden vs Tunisia</t>
         </is>
       </c>
-      <c r="B402" s="18" t="inlineStr">
-        <is>
-          <t>Goals O/U 1.5</t>
-        </is>
-      </c>
-      <c r="C402" s="5" t="inlineStr">
+      <c r="B402" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 1.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C402" s="23" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="D402" s="15" t="inlineStr">
+      <c r="D402" s="23" t="inlineStr">
         <is>
           <t>72.0%</t>
         </is>
       </c>
-      <c r="E402" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F402" s="5" t="inlineStr">
+      <c r="E402" s="23" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="F402" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G402" s="5" t="inlineStr">
+      <c r="G402" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="E411" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F411" s="3" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="E414" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="F414" s="5" t="inlineStr">
@@ -18039,7 +18039,7 @@
       </c>
       <c r="C416" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D416" s="12" t="inlineStr">
@@ -18463,7 +18463,7 @@
       </c>
       <c r="E429" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="F429" s="3" t="inlineStr">
@@ -18478,37 +18478,37 @@
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
-      <c r="A430" s="18" t="inlineStr">
+      <c r="A430" s="22" t="inlineStr">
         <is>
           <t>Spain vs Cape Verde</t>
         </is>
       </c>
-      <c r="B430" s="18" t="inlineStr">
-        <is>
-          <t>Draw No Bet Spain</t>
-        </is>
-      </c>
-      <c r="C430" s="5" t="inlineStr">
-        <is>
-          <t>Victorie</t>
-        </is>
-      </c>
-      <c r="D430" s="4" t="inlineStr">
+      <c r="B430" s="22" t="inlineStr">
+        <is>
+          <t>Draw No Bet Spain *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C430" s="23" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="D430" s="23" t="inlineStr">
         <is>
           <t>93.6%</t>
         </is>
       </c>
-      <c r="E430" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F430" s="5" t="inlineStr">
+      <c r="E430" s="23" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="F430" s="23" t="inlineStr">
         <is>
           <t>dnb</t>
         </is>
       </c>
-      <c r="G430" s="5" t="inlineStr">
+      <c r="G430" s="23" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -18685,7 +18685,7 @@
       </c>
       <c r="E435" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="F435" s="3" t="inlineStr">
@@ -18737,37 +18737,37 @@
       </c>
     </row>
     <row r="437" ht="15" customHeight="1">
-      <c r="A437" s="22" t="inlineStr">
+      <c r="A437" s="17" t="inlineStr">
         <is>
           <t>Spain vs Cape Verde</t>
         </is>
       </c>
-      <c r="B437" s="22" t="inlineStr">
-        <is>
-          <t>1X2 Result *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C437" s="23" t="inlineStr">
+      <c r="B437" s="17" t="inlineStr">
+        <is>
+          <t>1X2 Result</t>
+        </is>
+      </c>
+      <c r="C437" s="3" t="inlineStr">
         <is>
           <t>1 (Spain)</t>
         </is>
       </c>
-      <c r="D437" s="23" t="inlineStr">
+      <c r="D437" s="4" t="inlineStr">
         <is>
           <t>82.4%</t>
         </is>
       </c>
-      <c r="E437" s="23" t="inlineStr">
+      <c r="E437" s="3" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="F437" s="23" t="inlineStr">
+      <c r="F437" s="3" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="G437" s="23" t="inlineStr">
+      <c r="G437" s="3" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -18796,7 +18796,7 @@
       </c>
       <c r="E438" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="F438" s="5" t="inlineStr">
@@ -18848,37 +18848,37 @@
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
-      <c r="A440" s="18" t="inlineStr">
+      <c r="A440" s="22" t="inlineStr">
         <is>
           <t>Spain vs Cape Verde</t>
         </is>
       </c>
-      <c r="B440" s="18" t="inlineStr">
-        <is>
-          <t>Goals O/U 3.5</t>
-        </is>
-      </c>
-      <c r="C440" s="5" t="inlineStr">
+      <c r="B440" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 3.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C440" s="23" t="inlineStr">
         <is>
           <t>Under 3.5</t>
         </is>
       </c>
-      <c r="D440" s="15" t="inlineStr">
+      <c r="D440" s="23" t="inlineStr">
         <is>
           <t>72.8%</t>
         </is>
       </c>
-      <c r="E440" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F440" s="5" t="inlineStr">
+      <c r="E440" s="23" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="F440" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G440" s="5" t="inlineStr">
+      <c r="G440" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -19033,37 +19033,37 @@
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
-      <c r="A445" s="22" t="inlineStr">
+      <c r="A445" s="17" t="inlineStr">
         <is>
           <t>Spain vs Cape Verde</t>
         </is>
       </c>
-      <c r="B445" s="22" t="inlineStr">
-        <is>
-          <t>GG (Both Teams Score) *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C445" s="23" t="inlineStr">
+      <c r="B445" s="17" t="inlineStr">
+        <is>
+          <t>GG (Both Teams Score)</t>
+        </is>
+      </c>
+      <c r="C445" s="3" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="D445" s="23" t="inlineStr">
+      <c r="D445" s="15" t="inlineStr">
         <is>
           <t>62.5%</t>
         </is>
       </c>
-      <c r="E445" s="23" t="inlineStr">
+      <c r="E445" s="3" t="inlineStr">
         <is>
           <t>1.44</t>
         </is>
       </c>
-      <c r="F445" s="23" t="inlineStr">
+      <c r="F445" s="3" t="inlineStr">
         <is>
           <t>gg</t>
         </is>
       </c>
-      <c r="G445" s="23" t="inlineStr">
+      <c r="G445" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E449" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="F449" s="3" t="inlineStr">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="E452" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F452" s="5" t="inlineStr">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C459" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D459" s="12" t="inlineStr">
@@ -19573,7 +19573,7 @@
       </c>
       <c r="E459" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="F459" s="3" t="inlineStr">
@@ -19706,37 +19706,37 @@
       </c>
     </row>
     <row r="465" ht="15" customHeight="1">
-      <c r="A465" s="22" t="inlineStr">
+      <c r="A465" s="17" t="inlineStr">
         <is>
           <t>Belgium vs Egypt</t>
         </is>
       </c>
-      <c r="B465" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C465" s="23" t="inlineStr">
+      <c r="B465" s="17" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C465" s="3" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D465" s="23" t="inlineStr">
+      <c r="D465" s="4" t="inlineStr">
         <is>
           <t>91.9%</t>
         </is>
       </c>
-      <c r="E465" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F465" s="23" t="inlineStr">
+      <c r="E465" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F465" s="3" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G465" s="23" t="inlineStr">
+      <c r="G465" s="3" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="E466" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F466" s="5" t="inlineStr">
@@ -19792,7 +19792,7 @@
       </c>
       <c r="C467" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D467" s="4" t="inlineStr">
@@ -19802,7 +19802,7 @@
       </c>
       <c r="E467" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F467" s="3" t="inlineStr">
@@ -19839,7 +19839,7 @@
       </c>
       <c r="E468" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F468" s="5" t="inlineStr">
@@ -20024,7 +20024,7 @@
       </c>
       <c r="E473" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F473" s="3" t="inlineStr">
@@ -20039,37 +20039,37 @@
       </c>
     </row>
     <row r="474" ht="15" customHeight="1">
-      <c r="A474" s="18" t="inlineStr">
+      <c r="A474" s="22" t="inlineStr">
         <is>
           <t>Belgium vs Egypt</t>
         </is>
       </c>
-      <c r="B474" s="18" t="inlineStr">
-        <is>
-          <t>Goals O/U 3.5</t>
-        </is>
-      </c>
-      <c r="C474" s="5" t="inlineStr">
+      <c r="B474" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 3.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C474" s="23" t="inlineStr">
         <is>
           <t>Under 3.5</t>
         </is>
       </c>
-      <c r="D474" s="15" t="inlineStr">
+      <c r="D474" s="23" t="inlineStr">
         <is>
           <t>73.6%</t>
         </is>
       </c>
-      <c r="E474" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F474" s="5" t="inlineStr">
+      <c r="E474" s="23" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F474" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G474" s="5" t="inlineStr">
+      <c r="G474" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -20468,7 +20468,7 @@
       </c>
       <c r="E485" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="F485" s="3" t="inlineStr">
@@ -20616,7 +20616,7 @@
       </c>
       <c r="E489" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="F489" s="3" t="inlineStr">
@@ -20791,7 +20791,7 @@
       </c>
       <c r="C494" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D494" s="12" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="E494" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F494" s="5" t="inlineStr">
@@ -21045,37 +21045,37 @@
       </c>
     </row>
     <row r="503" ht="15" customHeight="1">
-      <c r="A503" s="22" t="inlineStr">
+      <c r="A503" s="17" t="inlineStr">
         <is>
           <t>Saudi Arabia vs Uruguay</t>
         </is>
       </c>
-      <c r="B503" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C503" s="23" t="inlineStr">
+      <c r="B503" s="17" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C503" s="3" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D503" s="23" t="inlineStr">
+      <c r="D503" s="4" t="inlineStr">
         <is>
           <t>91.4%</t>
         </is>
       </c>
-      <c r="E503" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F503" s="23" t="inlineStr">
+      <c r="E503" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F503" s="3" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G503" s="23" t="inlineStr">
+      <c r="G503" s="3" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -21104,7 +21104,7 @@
       </c>
       <c r="E504" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="F504" s="23" t="inlineStr">
@@ -21205,7 +21205,7 @@
       </c>
       <c r="C507" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D507" s="4" t="inlineStr">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="E507" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F507" s="3" t="inlineStr">
@@ -21267,37 +21267,37 @@
       </c>
     </row>
     <row r="509" ht="15" customHeight="1">
-      <c r="A509" s="17" t="inlineStr">
+      <c r="A509" s="22" t="inlineStr">
         <is>
           <t>Saudi Arabia vs Uruguay</t>
         </is>
       </c>
-      <c r="B509" s="17" t="inlineStr">
-        <is>
-          <t>Goals O/U 3.5</t>
-        </is>
-      </c>
-      <c r="C509" s="3" t="inlineStr">
+      <c r="B509" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 3.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C509" s="23" t="inlineStr">
         <is>
           <t>Under 3.5</t>
         </is>
       </c>
-      <c r="D509" s="15" t="inlineStr">
+      <c r="D509" s="23" t="inlineStr">
         <is>
           <t>74.8%</t>
         </is>
       </c>
-      <c r="E509" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F509" s="3" t="inlineStr">
+      <c r="E509" s="23" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="F509" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G509" s="3" t="inlineStr">
+      <c r="G509" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -21326,7 +21326,7 @@
       </c>
       <c r="E510" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F510" s="5" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="E513" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="F513" s="3" t="inlineStr">
@@ -21696,7 +21696,7 @@
       </c>
       <c r="E520" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="F520" s="5" t="inlineStr">
@@ -21844,7 +21844,7 @@
       </c>
       <c r="E524" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="F524" s="5" t="inlineStr">
@@ -22019,7 +22019,7 @@
       </c>
       <c r="C529" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D529" s="12" t="inlineStr">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="E529" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="F529" s="3" t="inlineStr">
@@ -22384,37 +22384,37 @@
       </c>
     </row>
     <row r="541" ht="15" customHeight="1">
-      <c r="A541" s="22" t="inlineStr">
+      <c r="A541" s="17" t="inlineStr">
         <is>
           <t>Iran vs New Zealand</t>
         </is>
       </c>
-      <c r="B541" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C541" s="23" t="inlineStr">
+      <c r="B541" s="17" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C541" s="3" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D541" s="23" t="inlineStr">
+      <c r="D541" s="4" t="inlineStr">
         <is>
           <t>92.1%</t>
         </is>
       </c>
-      <c r="E541" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F541" s="23" t="inlineStr">
+      <c r="E541" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F541" s="3" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G541" s="23" t="inlineStr">
+      <c r="G541" s="3" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="E542" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F542" s="5" t="inlineStr">
@@ -22470,7 +22470,7 @@
       </c>
       <c r="C543" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D543" s="4" t="inlineStr">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="E543" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F543" s="3" t="inlineStr">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="E544" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F544" s="5" t="inlineStr">
@@ -22606,37 +22606,37 @@
       </c>
     </row>
     <row r="547" ht="15" customHeight="1">
-      <c r="A547" s="17" t="inlineStr">
+      <c r="A547" s="22" t="inlineStr">
         <is>
           <t>Iran vs New Zealand</t>
         </is>
       </c>
-      <c r="B547" s="17" t="inlineStr">
-        <is>
-          <t>Goals O/U 1.5</t>
-        </is>
-      </c>
-      <c r="C547" s="3" t="inlineStr">
+      <c r="B547" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 1.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C547" s="23" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="D547" s="15" t="inlineStr">
+      <c r="D547" s="23" t="inlineStr">
         <is>
           <t>74.8%</t>
         </is>
       </c>
-      <c r="E547" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F547" s="3" t="inlineStr">
+      <c r="E547" s="23" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="F547" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G547" s="3" t="inlineStr">
+      <c r="G547" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -22665,7 +22665,7 @@
       </c>
       <c r="E548" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F548" s="5" t="inlineStr">
@@ -23072,7 +23072,7 @@
       </c>
       <c r="E559" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F559" s="3" t="inlineStr">
@@ -23220,7 +23220,7 @@
       </c>
       <c r="E563" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="F563" s="3" t="inlineStr">
@@ -23358,7 +23358,7 @@
       </c>
       <c r="C567" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D567" s="12" t="inlineStr">
@@ -23368,7 +23368,7 @@
       </c>
       <c r="E567" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="F567" s="3" t="inlineStr">
@@ -23760,37 +23760,37 @@
       </c>
     </row>
     <row r="580" ht="15" customHeight="1">
-      <c r="A580" s="22" t="inlineStr">
+      <c r="A580" s="18" t="inlineStr">
         <is>
           <t>France vs Senegal</t>
         </is>
       </c>
-      <c r="B580" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C580" s="23" t="inlineStr">
+      <c r="B580" s="18" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C580" s="5" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D580" s="23" t="inlineStr">
+      <c r="D580" s="4" t="inlineStr">
         <is>
           <t>91.6%</t>
         </is>
       </c>
-      <c r="E580" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F580" s="23" t="inlineStr">
+      <c r="E580" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F580" s="5" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G580" s="23" t="inlineStr">
+      <c r="G580" s="5" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -23819,7 +23819,7 @@
       </c>
       <c r="E581" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="F581" s="23" t="inlineStr">
@@ -23957,7 +23957,7 @@
       </c>
       <c r="C585" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D585" s="4" t="inlineStr">
@@ -23982,37 +23982,37 @@
       </c>
     </row>
     <row r="586" ht="15" customHeight="1">
-      <c r="A586" s="18" t="inlineStr">
+      <c r="A586" s="22" t="inlineStr">
         <is>
           <t>France vs Senegal</t>
         </is>
       </c>
-      <c r="B586" s="18" t="inlineStr">
-        <is>
-          <t>Goals O/U 3.5</t>
-        </is>
-      </c>
-      <c r="C586" s="5" t="inlineStr">
+      <c r="B586" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 3.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C586" s="23" t="inlineStr">
         <is>
           <t>Under 3.5</t>
         </is>
       </c>
-      <c r="D586" s="15" t="inlineStr">
+      <c r="D586" s="23" t="inlineStr">
         <is>
           <t>74.3%</t>
         </is>
       </c>
-      <c r="E586" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F586" s="5" t="inlineStr">
+      <c r="E586" s="23" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F586" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G586" s="5" t="inlineStr">
+      <c r="G586" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -24078,7 +24078,7 @@
       </c>
       <c r="E588" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F588" s="5" t="inlineStr">
@@ -24189,7 +24189,7 @@
       </c>
       <c r="E591" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F591" s="3" t="inlineStr">
@@ -24448,7 +24448,7 @@
       </c>
       <c r="E598" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="F598" s="5" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="E600" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="F600" s="5" t="inlineStr">
@@ -24660,7 +24660,7 @@
       </c>
       <c r="C604" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D604" s="12" t="inlineStr">
@@ -25025,74 +25025,74 @@
       </c>
     </row>
     <row r="616" ht="15" customHeight="1">
-      <c r="A616" s="22" t="inlineStr">
+      <c r="A616" s="18" t="inlineStr">
         <is>
           <t>Iraq vs Norway</t>
         </is>
       </c>
-      <c r="B616" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C616" s="23" t="inlineStr">
+      <c r="B616" s="18" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C616" s="5" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D616" s="23" t="inlineStr">
+      <c r="D616" s="4" t="inlineStr">
         <is>
           <t>92.1%</t>
         </is>
       </c>
-      <c r="E616" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F616" s="23" t="inlineStr">
+      <c r="E616" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F616" s="5" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G616" s="23" t="inlineStr">
+      <c r="G616" s="5" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
     </row>
     <row r="617" ht="15" customHeight="1">
-      <c r="A617" s="17" t="inlineStr">
+      <c r="A617" s="22" t="inlineStr">
         <is>
           <t>Iraq vs Norway</t>
         </is>
       </c>
-      <c r="B617" s="17" t="inlineStr">
-        <is>
-          <t>Double Chance X2</t>
-        </is>
-      </c>
-      <c r="C617" s="3" t="inlineStr">
+      <c r="B617" s="22" t="inlineStr">
+        <is>
+          <t>Double Chance X2 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C617" s="23" t="inlineStr">
         <is>
           <t>X2</t>
         </is>
       </c>
-      <c r="D617" s="4" t="inlineStr">
+      <c r="D617" s="23" t="inlineStr">
         <is>
           <t>91.6%</t>
         </is>
       </c>
-      <c r="E617" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F617" s="3" t="inlineStr">
+      <c r="E617" s="23" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="F617" s="23" t="inlineStr">
         <is>
           <t>dc</t>
         </is>
       </c>
-      <c r="G617" s="3" t="inlineStr">
+      <c r="G617" s="23" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -25111,7 +25111,7 @@
       </c>
       <c r="C618" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D618" s="4" t="inlineStr">
@@ -25121,7 +25121,7 @@
       </c>
       <c r="E618" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="F618" s="5" t="inlineStr">
@@ -25306,7 +25306,7 @@
       </c>
       <c r="E623" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="F623" s="3" t="inlineStr">
@@ -25417,7 +25417,7 @@
       </c>
       <c r="E626" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="F626" s="5" t="inlineStr">
@@ -25432,74 +25432,74 @@
       </c>
     </row>
     <row r="627" ht="15" customHeight="1">
-      <c r="A627" s="17" t="inlineStr">
+      <c r="A627" s="22" t="inlineStr">
         <is>
           <t>Iraq vs Norway</t>
         </is>
       </c>
-      <c r="B627" s="17" t="inlineStr">
-        <is>
-          <t>Goals O/U 3.5</t>
-        </is>
-      </c>
-      <c r="C627" s="3" t="inlineStr">
+      <c r="B627" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 3.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C627" s="23" t="inlineStr">
         <is>
           <t>Under 3.5</t>
         </is>
       </c>
-      <c r="D627" s="15" t="inlineStr">
+      <c r="D627" s="23" t="inlineStr">
         <is>
           <t>73.0%</t>
         </is>
       </c>
-      <c r="E627" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F627" s="3" t="inlineStr">
+      <c r="E627" s="23" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="F627" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G627" s="3" t="inlineStr">
+      <c r="G627" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="628" ht="15" customHeight="1">
-      <c r="A628" s="22" t="inlineStr">
+      <c r="A628" s="18" t="inlineStr">
         <is>
           <t>Iraq vs Norway</t>
         </is>
       </c>
-      <c r="B628" s="22" t="inlineStr">
-        <is>
-          <t>1X2 Result *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C628" s="23" t="inlineStr">
+      <c r="B628" s="18" t="inlineStr">
+        <is>
+          <t>1X2 Result</t>
+        </is>
+      </c>
+      <c r="C628" s="5" t="inlineStr">
         <is>
           <t>2 (Norway)</t>
         </is>
       </c>
-      <c r="D628" s="23" t="inlineStr">
+      <c r="D628" s="15" t="inlineStr">
         <is>
           <t>71.5%</t>
         </is>
       </c>
-      <c r="E628" s="23" t="inlineStr">
+      <c r="E628" s="5" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="F628" s="23" t="inlineStr">
+      <c r="F628" s="5" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="G628" s="23" t="inlineStr">
+      <c r="G628" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -25787,7 +25787,7 @@
       </c>
       <c r="E636" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="F636" s="5" t="inlineStr">
@@ -25898,7 +25898,7 @@
       </c>
       <c r="E639" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F639" s="3" t="inlineStr">
@@ -26073,7 +26073,7 @@
       </c>
       <c r="C644" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D644" s="12" t="inlineStr">
@@ -26083,7 +26083,7 @@
       </c>
       <c r="E644" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F644" s="5" t="inlineStr">
@@ -26327,37 +26327,37 @@
       </c>
     </row>
     <row r="653" ht="15" customHeight="1">
-      <c r="A653" s="22" t="inlineStr">
+      <c r="A653" s="17" t="inlineStr">
         <is>
           <t>Argentina vs Algeria</t>
         </is>
       </c>
-      <c r="B653" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C653" s="23" t="inlineStr">
+      <c r="B653" s="17" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C653" s="3" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D653" s="23" t="inlineStr">
+      <c r="D653" s="4" t="inlineStr">
         <is>
           <t>90.8%</t>
         </is>
       </c>
-      <c r="E653" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F653" s="23" t="inlineStr">
+      <c r="E653" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F653" s="3" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G653" s="23" t="inlineStr">
+      <c r="G653" s="3" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -26386,7 +26386,7 @@
       </c>
       <c r="E654" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="F654" s="5" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="C655" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D655" s="4" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="E658" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F658" s="5" t="inlineStr">
@@ -26645,7 +26645,7 @@
       </c>
       <c r="E661" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F661" s="3" t="inlineStr">
@@ -26719,7 +26719,7 @@
       </c>
       <c r="E663" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F663" s="3" t="inlineStr">
@@ -26882,37 +26882,37 @@
       </c>
     </row>
     <row r="668" ht="15" customHeight="1">
-      <c r="A668" s="18" t="inlineStr">
+      <c r="A668" s="22" t="inlineStr">
         <is>
           <t>Argentina vs Algeria</t>
         </is>
       </c>
-      <c r="B668" s="18" t="inlineStr">
-        <is>
-          <t>Goals O/U 2.5</t>
-        </is>
-      </c>
-      <c r="C668" s="5" t="inlineStr">
+      <c r="B668" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 2.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C668" s="23" t="inlineStr">
         <is>
           <t>Under 2.5</t>
         </is>
       </c>
-      <c r="D668" s="11" t="inlineStr">
+      <c r="D668" s="23" t="inlineStr">
         <is>
           <t>55.2%</t>
         </is>
       </c>
-      <c r="E668" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F668" s="5" t="inlineStr">
+      <c r="E668" s="23" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="F668" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G668" s="5" t="inlineStr">
+      <c r="G668" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -27163,7 +27163,7 @@
       </c>
       <c r="E675" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F675" s="3" t="inlineStr">
@@ -27375,7 +27375,7 @@
       </c>
       <c r="C681" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D681" s="12" t="inlineStr">
@@ -27666,74 +27666,74 @@
       </c>
     </row>
     <row r="691" ht="15" customHeight="1">
-      <c r="A691" s="22" t="inlineStr">
+      <c r="A691" s="17" t="inlineStr">
         <is>
           <t>Austria vs Jordan</t>
         </is>
       </c>
-      <c r="B691" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C691" s="23" t="inlineStr">
+      <c r="B691" s="17" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C691" s="3" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D691" s="23" t="inlineStr">
+      <c r="D691" s="4" t="inlineStr">
         <is>
           <t>91.9%</t>
         </is>
       </c>
-      <c r="E691" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F691" s="23" t="inlineStr">
+      <c r="E691" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F691" s="3" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G691" s="23" t="inlineStr">
+      <c r="G691" s="3" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
     </row>
     <row r="692" ht="15" customHeight="1">
-      <c r="A692" s="22" t="inlineStr">
+      <c r="A692" s="18" t="inlineStr">
         <is>
           <t>Austria vs Jordan</t>
         </is>
       </c>
-      <c r="B692" s="22" t="inlineStr">
-        <is>
-          <t>Double Chance 1X *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C692" s="23" t="inlineStr">
+      <c r="B692" s="18" t="inlineStr">
+        <is>
+          <t>Double Chance 1X</t>
+        </is>
+      </c>
+      <c r="C692" s="5" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="D692" s="23" t="inlineStr">
+      <c r="D692" s="4" t="inlineStr">
         <is>
           <t>86.4%</t>
         </is>
       </c>
-      <c r="E692" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F692" s="23" t="inlineStr">
+      <c r="E692" s="5" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="F692" s="5" t="inlineStr">
         <is>
           <t>dc</t>
         </is>
       </c>
-      <c r="G692" s="23" t="inlineStr">
+      <c r="G692" s="5" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="C696" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D696" s="4" t="inlineStr">
@@ -27873,7 +27873,7 @@
       </c>
       <c r="E696" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F696" s="5" t="inlineStr">
@@ -27947,7 +27947,7 @@
       </c>
       <c r="E698" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="F698" s="5" t="inlineStr">
@@ -27999,37 +27999,37 @@
       </c>
     </row>
     <row r="700" ht="15" customHeight="1">
-      <c r="A700" s="18" t="inlineStr">
+      <c r="A700" s="22" t="inlineStr">
         <is>
           <t>Austria vs Jordan</t>
         </is>
       </c>
-      <c r="B700" s="18" t="inlineStr">
-        <is>
-          <t>Goals O/U 3.5</t>
-        </is>
-      </c>
-      <c r="C700" s="5" t="inlineStr">
+      <c r="B700" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 3.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C700" s="23" t="inlineStr">
         <is>
           <t>Under 3.5</t>
         </is>
       </c>
-      <c r="D700" s="15" t="inlineStr">
+      <c r="D700" s="23" t="inlineStr">
         <is>
           <t>73.6%</t>
         </is>
       </c>
-      <c r="E700" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F700" s="5" t="inlineStr">
+      <c r="E700" s="23" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="F700" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G700" s="5" t="inlineStr">
+      <c r="G700" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -28169,7 +28169,7 @@
       </c>
       <c r="E704" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F704" s="5" t="inlineStr">
@@ -28184,37 +28184,37 @@
       </c>
     </row>
     <row r="705" ht="15" customHeight="1">
-      <c r="A705" s="17" t="inlineStr">
+      <c r="A705" s="22" t="inlineStr">
         <is>
           <t>Austria vs Jordan</t>
         </is>
       </c>
-      <c r="B705" s="17" t="inlineStr">
-        <is>
-          <t>Double Chance X2</t>
-        </is>
-      </c>
-      <c r="C705" s="3" t="inlineStr">
+      <c r="B705" s="22" t="inlineStr">
+        <is>
+          <t>Double Chance X2 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C705" s="23" t="inlineStr">
         <is>
           <t>X2</t>
         </is>
       </c>
-      <c r="D705" s="11" t="inlineStr">
+      <c r="D705" s="23" t="inlineStr">
         <is>
           <t>55.5%</t>
         </is>
       </c>
-      <c r="E705" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F705" s="3" t="inlineStr">
+      <c r="E705" s="23" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="F705" s="23" t="inlineStr">
         <is>
           <t>dc</t>
         </is>
       </c>
-      <c r="G705" s="3" t="inlineStr">
+      <c r="G705" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -28317,7 +28317,7 @@
       </c>
       <c r="E708" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="F708" s="5" t="inlineStr">
@@ -28640,7 +28640,7 @@
       </c>
       <c r="C717" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D717" s="12" t="inlineStr">
@@ -28650,7 +28650,7 @@
       </c>
       <c r="E717" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="F717" s="3" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="E729" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="F729" s="3" t="inlineStr">
@@ -29079,37 +29079,37 @@
       </c>
     </row>
     <row r="731" ht="15" customHeight="1">
-      <c r="A731" s="17" t="inlineStr">
+      <c r="A731" s="22" t="inlineStr">
         <is>
           <t>Portugal vs DR Congo</t>
         </is>
       </c>
-      <c r="B731" s="17" t="inlineStr">
-        <is>
-          <t>Draw No Bet Portugal</t>
-        </is>
-      </c>
-      <c r="C731" s="3" t="inlineStr">
-        <is>
-          <t>Victorie</t>
-        </is>
-      </c>
-      <c r="D731" s="4" t="inlineStr">
+      <c r="B731" s="22" t="inlineStr">
+        <is>
+          <t>Draw No Bet Portugal *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C731" s="23" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="D731" s="23" t="inlineStr">
         <is>
           <t>90.0%</t>
         </is>
       </c>
-      <c r="E731" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F731" s="3" t="inlineStr">
+      <c r="E731" s="23" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="F731" s="23" t="inlineStr">
         <is>
           <t>dnb</t>
         </is>
       </c>
-      <c r="G731" s="3" t="inlineStr">
+      <c r="G731" s="23" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -29323,7 +29323,7 @@
       </c>
       <c r="E737" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="F737" s="3" t="inlineStr">
@@ -29375,37 +29375,37 @@
       </c>
     </row>
     <row r="739" ht="15" customHeight="1">
-      <c r="A739" s="17" t="inlineStr">
+      <c r="A739" s="22" t="inlineStr">
         <is>
           <t>Portugal vs DR Congo</t>
         </is>
       </c>
-      <c r="B739" s="17" t="inlineStr">
-        <is>
-          <t>Goals O/U 1.5</t>
-        </is>
-      </c>
-      <c r="C739" s="3" t="inlineStr">
+      <c r="B739" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 1.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C739" s="23" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="D739" s="15" t="inlineStr">
+      <c r="D739" s="23" t="inlineStr">
         <is>
           <t>74.4%</t>
         </is>
       </c>
-      <c r="E739" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F739" s="3" t="inlineStr">
+      <c r="E739" s="23" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="F739" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G739" s="3" t="inlineStr">
+      <c r="G739" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="E740" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F740" s="5" t="inlineStr">
@@ -29449,37 +29449,37 @@
       </c>
     </row>
     <row r="741" ht="15" customHeight="1">
-      <c r="A741" s="22" t="inlineStr">
+      <c r="A741" s="17" t="inlineStr">
         <is>
           <t>Portugal vs DR Congo</t>
         </is>
       </c>
-      <c r="B741" s="22" t="inlineStr">
-        <is>
-          <t>1X2 Result *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C741" s="23" t="inlineStr">
+      <c r="B741" s="17" t="inlineStr">
+        <is>
+          <t>1X2 Result</t>
+        </is>
+      </c>
+      <c r="C741" s="3" t="inlineStr">
         <is>
           <t>1 (Portugal)</t>
         </is>
       </c>
-      <c r="D741" s="23" t="inlineStr">
+      <c r="D741" s="15" t="inlineStr">
         <is>
           <t>68.1%</t>
         </is>
       </c>
-      <c r="E741" s="23" t="inlineStr">
+      <c r="E741" s="3" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="F741" s="23" t="inlineStr">
+      <c r="F741" s="3" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="G741" s="23" t="inlineStr">
+      <c r="G741" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -29634,37 +29634,37 @@
       </c>
     </row>
     <row r="746" ht="15" customHeight="1">
-      <c r="A746" s="22" t="inlineStr">
+      <c r="A746" s="18" t="inlineStr">
         <is>
           <t>Portugal vs DR Congo</t>
         </is>
       </c>
-      <c r="B746" s="22" t="inlineStr">
-        <is>
-          <t>GG (Both Teams Score) *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C746" s="23" t="inlineStr">
+      <c r="B746" s="18" t="inlineStr">
+        <is>
+          <t>GG (Both Teams Score)</t>
+        </is>
+      </c>
+      <c r="C746" s="5" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="D746" s="23" t="inlineStr">
+      <c r="D746" s="11" t="inlineStr">
         <is>
           <t>55.2%</t>
         </is>
       </c>
-      <c r="E746" s="23" t="inlineStr">
+      <c r="E746" s="5" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="F746" s="23" t="inlineStr">
+      <c r="F746" s="5" t="inlineStr">
         <is>
           <t>gg</t>
         </is>
       </c>
-      <c r="G746" s="23" t="inlineStr">
+      <c r="G746" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -29767,7 +29767,7 @@
       </c>
       <c r="E749" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="F749" s="3" t="inlineStr">
@@ -29841,7 +29841,7 @@
       </c>
       <c r="E751" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="F751" s="3" t="inlineStr">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C756" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D756" s="12" t="inlineStr">
@@ -30026,7 +30026,7 @@
       </c>
       <c r="E756" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F756" s="5" t="inlineStr">
@@ -30270,37 +30270,37 @@
       </c>
     </row>
     <row r="765" ht="15" customHeight="1">
-      <c r="A765" s="22" t="inlineStr">
+      <c r="A765" s="17" t="inlineStr">
         <is>
           <t>England vs Croatia</t>
         </is>
       </c>
-      <c r="B765" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C765" s="23" t="inlineStr">
+      <c r="B765" s="17" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C765" s="3" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D765" s="23" t="inlineStr">
+      <c r="D765" s="4" t="inlineStr">
         <is>
           <t>91.3%</t>
         </is>
       </c>
-      <c r="E765" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F765" s="23" t="inlineStr">
+      <c r="E765" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F765" s="3" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G765" s="23" t="inlineStr">
+      <c r="G765" s="3" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -30329,7 +30329,7 @@
       </c>
       <c r="E766" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F766" s="5" t="inlineStr">
@@ -30381,37 +30381,37 @@
       </c>
     </row>
     <row r="768" ht="15" customHeight="1">
-      <c r="A768" s="18" t="inlineStr">
+      <c r="A768" s="22" t="inlineStr">
         <is>
           <t>England vs Croatia</t>
         </is>
       </c>
-      <c r="B768" s="18" t="inlineStr">
-        <is>
-          <t>Draw No Bet England</t>
-        </is>
-      </c>
-      <c r="C768" s="5" t="inlineStr">
-        <is>
-          <t>Victorie</t>
-        </is>
-      </c>
-      <c r="D768" s="4" t="inlineStr">
+      <c r="B768" s="22" t="inlineStr">
+        <is>
+          <t>Draw No Bet England *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C768" s="23" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="D768" s="23" t="inlineStr">
         <is>
           <t>82.3%</t>
         </is>
       </c>
-      <c r="E768" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F768" s="5" t="inlineStr">
+      <c r="E768" s="23" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F768" s="23" t="inlineStr">
         <is>
           <t>dnb</t>
         </is>
       </c>
-      <c r="G768" s="5" t="inlineStr">
+      <c r="G768" s="23" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="E771" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F771" s="3" t="inlineStr">
@@ -30588,7 +30588,7 @@
       </c>
       <c r="E773" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F773" s="3" t="inlineStr">
@@ -30603,37 +30603,37 @@
       </c>
     </row>
     <row r="774" ht="15" customHeight="1">
-      <c r="A774" s="18" t="inlineStr">
+      <c r="A774" s="22" t="inlineStr">
         <is>
           <t>England vs Croatia</t>
         </is>
       </c>
-      <c r="B774" s="18" t="inlineStr">
-        <is>
-          <t>Goals O/U 1.5</t>
-        </is>
-      </c>
-      <c r="C774" s="5" t="inlineStr">
+      <c r="B774" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 1.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C774" s="23" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="D774" s="15" t="inlineStr">
+      <c r="D774" s="23" t="inlineStr">
         <is>
           <t>72.8%</t>
         </is>
       </c>
-      <c r="E774" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F774" s="5" t="inlineStr">
+      <c r="E774" s="23" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="F774" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G774" s="5" t="inlineStr">
+      <c r="G774" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -30751,37 +30751,37 @@
       </c>
     </row>
     <row r="778" ht="15" customHeight="1">
-      <c r="A778" s="22" t="inlineStr">
+      <c r="A778" s="18" t="inlineStr">
         <is>
           <t>England vs Croatia</t>
         </is>
       </c>
-      <c r="B778" s="22" t="inlineStr">
-        <is>
-          <t>1X2 Result *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C778" s="23" t="inlineStr">
+      <c r="B778" s="18" t="inlineStr">
+        <is>
+          <t>1X2 Result</t>
+        </is>
+      </c>
+      <c r="C778" s="5" t="inlineStr">
         <is>
           <t>1 (England)</t>
         </is>
       </c>
-      <c r="D778" s="23" t="inlineStr">
+      <c r="D778" s="15" t="inlineStr">
         <is>
           <t>62.8%</t>
         </is>
       </c>
-      <c r="E778" s="23" t="inlineStr">
+      <c r="E778" s="5" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="F778" s="23" t="inlineStr">
+      <c r="F778" s="5" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="G778" s="23" t="inlineStr">
+      <c r="G778" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -30958,7 +30958,7 @@
       </c>
       <c r="E783" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F783" s="3" t="inlineStr">
@@ -31069,7 +31069,7 @@
       </c>
       <c r="E786" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="F786" s="5" t="inlineStr">
@@ -31170,7 +31170,7 @@
       </c>
       <c r="C789" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D789" s="12" t="inlineStr">
@@ -31180,7 +31180,7 @@
       </c>
       <c r="E789" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F789" s="3" t="inlineStr">
@@ -31535,37 +31535,37 @@
       </c>
     </row>
     <row r="801" ht="15" customHeight="1">
-      <c r="A801" s="22" t="inlineStr">
+      <c r="A801" s="17" t="inlineStr">
         <is>
           <t>Ghana vs Panama</t>
         </is>
       </c>
-      <c r="B801" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C801" s="23" t="inlineStr">
+      <c r="B801" s="17" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C801" s="3" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D801" s="23" t="inlineStr">
+      <c r="D801" s="4" t="inlineStr">
         <is>
           <t>91.9%</t>
         </is>
       </c>
-      <c r="E801" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F801" s="23" t="inlineStr">
+      <c r="E801" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F801" s="3" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G801" s="23" t="inlineStr">
+      <c r="G801" s="3" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -31594,7 +31594,7 @@
       </c>
       <c r="E802" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F802" s="23" t="inlineStr">
@@ -31683,37 +31683,37 @@
       </c>
     </row>
     <row r="805" ht="15" customHeight="1">
-      <c r="A805" s="17" t="inlineStr">
+      <c r="A805" s="22" t="inlineStr">
         <is>
           <t>Ghana vs Panama</t>
         </is>
       </c>
-      <c r="B805" s="17" t="inlineStr">
-        <is>
-          <t>Goals O/U 1.5</t>
-        </is>
-      </c>
-      <c r="C805" s="3" t="inlineStr">
+      <c r="B805" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 1.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C805" s="23" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="D805" s="15" t="inlineStr">
+      <c r="D805" s="23" t="inlineStr">
         <is>
           <t>74.3%</t>
         </is>
       </c>
-      <c r="E805" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F805" s="3" t="inlineStr">
+      <c r="E805" s="23" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="F805" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G805" s="3" t="inlineStr">
+      <c r="G805" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -31742,7 +31742,7 @@
       </c>
       <c r="E806" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F806" s="5" t="inlineStr">
@@ -31880,7 +31880,7 @@
       </c>
       <c r="C810" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D810" s="15" t="inlineStr">
@@ -31890,7 +31890,7 @@
       </c>
       <c r="E810" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F810" s="5" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="E812" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F812" s="5" t="inlineStr">
@@ -32186,7 +32186,7 @@
       </c>
       <c r="E818" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F818" s="5" t="inlineStr">
@@ -32260,7 +32260,7 @@
       </c>
       <c r="E820" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F820" s="5" t="inlineStr">
@@ -32324,7 +32324,7 @@
       </c>
       <c r="C822" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D822" s="12" t="inlineStr">
@@ -32334,7 +32334,7 @@
       </c>
       <c r="E822" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F822" s="5" t="inlineStr">
@@ -32763,37 +32763,37 @@
       </c>
     </row>
     <row r="836" ht="15" customHeight="1">
-      <c r="A836" s="22" t="inlineStr">
+      <c r="A836" s="18" t="inlineStr">
         <is>
           <t>Uzbekistan vs Colombia</t>
         </is>
       </c>
-      <c r="B836" s="22" t="inlineStr">
-        <is>
-          <t>Goals O/U 0.5 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C836" s="23" t="inlineStr">
+      <c r="B836" s="18" t="inlineStr">
+        <is>
+          <t>Goals O/U 0.5</t>
+        </is>
+      </c>
+      <c r="C836" s="5" t="inlineStr">
         <is>
           <t>Over 0.5</t>
         </is>
       </c>
-      <c r="D836" s="23" t="inlineStr">
+      <c r="D836" s="4" t="inlineStr">
         <is>
           <t>91.6%</t>
         </is>
       </c>
-      <c r="E836" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F836" s="23" t="inlineStr">
+      <c r="E836" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F836" s="5" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G836" s="23" t="inlineStr">
+      <c r="G836" s="5" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -32822,7 +32822,7 @@
       </c>
       <c r="E837" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="F837" s="23" t="inlineStr">
@@ -32923,7 +32923,7 @@
       </c>
       <c r="C840" s="5" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D840" s="4" t="inlineStr">
@@ -32933,7 +32933,7 @@
       </c>
       <c r="E840" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="F840" s="5" t="inlineStr">
@@ -32985,37 +32985,37 @@
       </c>
     </row>
     <row r="842" ht="15" customHeight="1">
-      <c r="A842" s="18" t="inlineStr">
+      <c r="A842" s="22" t="inlineStr">
         <is>
           <t>Uzbekistan vs Colombia</t>
         </is>
       </c>
-      <c r="B842" s="18" t="inlineStr">
-        <is>
-          <t>Goals O/U 3.5</t>
-        </is>
-      </c>
-      <c r="C842" s="5" t="inlineStr">
+      <c r="B842" s="22" t="inlineStr">
+        <is>
+          <t>Goals O/U 3.5 *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C842" s="23" t="inlineStr">
         <is>
           <t>Under 3.5</t>
         </is>
       </c>
-      <c r="D842" s="15" t="inlineStr">
+      <c r="D842" s="23" t="inlineStr">
         <is>
           <t>74.3%</t>
         </is>
       </c>
-      <c r="E842" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F842" s="5" t="inlineStr">
+      <c r="E842" s="23" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F842" s="23" t="inlineStr">
         <is>
           <t>goals_ou</t>
         </is>
       </c>
-      <c r="G842" s="5" t="inlineStr">
+      <c r="G842" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="E843" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F843" s="3" t="inlineStr">
@@ -33229,7 +33229,7 @@
       </c>
       <c r="E848" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F848" s="5" t="inlineStr">
@@ -33340,7 +33340,7 @@
       </c>
       <c r="E851" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F851" s="3" t="inlineStr">
@@ -33377,7 +33377,7 @@
       </c>
       <c r="E852" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="F852" s="5" t="inlineStr">
@@ -33700,7 +33700,7 @@
       </c>
       <c r="C861" s="3" t="inlineStr">
         <is>
-          <t>Victorie</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D861" s="12" t="inlineStr">
@@ -33710,7 +33710,7 @@
       </c>
       <c r="E861" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F861" s="3" t="inlineStr">
@@ -34280,22 +34280,22 @@
       </c>
       <c r="D7" s="25" t="inlineStr">
         <is>
-          <t>Fouls O/U 20.5</t>
+          <t>Double Chance 1X</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>Over 20.5</t>
+          <t>1X</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>fouls</t>
+          <t>dc</t>
         </is>
       </c>
     </row>
@@ -34317,17 +34317,17 @@
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Goals O/U 3.5</t>
         </is>
       </c>
       <c r="E8" s="26" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Under 3.5</t>
         </is>
       </c>
       <c r="F8" s="26" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="G8" s="26" t="inlineStr">
@@ -34354,22 +34354,22 @@
       </c>
       <c r="D9" s="29" t="inlineStr">
         <is>
-          <t>Double Chance 1X</t>
+          <t>Fouls O/U 20.5</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>1X</t>
+          <t>Over 20.5</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="G9" s="28" t="inlineStr">
         <is>
-          <t>dc</t>
+          <t>fouls</t>
         </is>
       </c>
     </row>
@@ -34391,22 +34391,22 @@
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Draw No Bet Canada</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>1 (Canada)</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>dnb</t>
         </is>
       </c>
     </row>
@@ -34428,17 +34428,17 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Goals O/U 1.5</t>
         </is>
       </c>
       <c r="E12" s="26" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="F12" s="26" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="G12" s="26" t="inlineStr">
@@ -34502,22 +34502,22 @@
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>GG (Both Teams Score)</t>
+          <t>Double Chance X2</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>Da</t>
+          <t>X2</t>
         </is>
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>gg</t>
+          <t>dc</t>
         </is>
       </c>
     </row>
@@ -34539,22 +34539,22 @@
       </c>
       <c r="D16" s="27" t="inlineStr">
         <is>
-          <t>Yellow Cards O/U 4.5</t>
+          <t>GG (Both Teams Score)</t>
         </is>
       </c>
       <c r="E16" s="26" t="inlineStr">
         <is>
-          <t>Under 4.5</t>
+          <t>Da</t>
         </is>
       </c>
       <c r="F16" s="26" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="G16" s="26" t="inlineStr">
         <is>
-          <t>yellows</t>
+          <t>gg</t>
         </is>
       </c>
     </row>
@@ -34576,22 +34576,22 @@
       </c>
       <c r="D17" s="29" t="inlineStr">
         <is>
-          <t>Fouls O/U 20.5</t>
+          <t>Yellow Cards O/U 4.5</t>
         </is>
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>Over 20.5</t>
+          <t>Under 4.5</t>
         </is>
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>79.9%</t>
         </is>
       </c>
       <c r="G17" s="28" t="inlineStr">
         <is>
-          <t>fouls</t>
+          <t>yellows</t>
         </is>
       </c>
     </row>
@@ -34650,22 +34650,22 @@
       </c>
       <c r="D20" s="27" t="inlineStr">
         <is>
-          <t>GG (Both Teams Score)</t>
+          <t>Goals O/U 3.5</t>
         </is>
       </c>
       <c r="E20" s="26" t="inlineStr">
         <is>
-          <t>Nu</t>
+          <t>Under 3.5</t>
         </is>
       </c>
       <c r="F20" s="26" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="G20" s="26" t="inlineStr">
         <is>
-          <t>gg</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -34761,17 +34761,17 @@
       </c>
       <c r="D24" s="27" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Goals O/U 1.5</t>
         </is>
       </c>
       <c r="E24" s="26" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="F24" s="26" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="G24" s="26" t="inlineStr">
@@ -34835,22 +34835,22 @@
       </c>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Goals O/U 1.5</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>2 (Scotland)</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -34872,22 +34872,22 @@
       </c>
       <c r="D28" s="27" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Double Chance X2</t>
         </is>
       </c>
       <c r="E28" s="26" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>X2</t>
         </is>
       </c>
       <c r="F28" s="26" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="G28" s="26" t="inlineStr">
         <is>
-          <t>goals_ou</t>
+          <t>dc</t>
         </is>
       </c>
     </row>
@@ -34983,17 +34983,17 @@
       </c>
       <c r="D32" s="27" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Goals O/U 1.5</t>
         </is>
       </c>
       <c r="E32" s="26" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="F32" s="26" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="G32" s="26" t="inlineStr">
@@ -35057,22 +35057,22 @@
       </c>
       <c r="D35" s="25" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Goals O/U 3.5</t>
         </is>
       </c>
       <c r="E35" s="24" t="inlineStr">
         <is>
-          <t>1 (Germany)</t>
+          <t>Under 3.5</t>
         </is>
       </c>
       <c r="F35" s="24" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="G35" s="24" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -35094,22 +35094,22 @@
       </c>
       <c r="D36" s="27" t="inlineStr">
         <is>
-          <t>GG (Both Teams Score)</t>
+          <t>Double Chance 1X</t>
         </is>
       </c>
       <c r="E36" s="26" t="inlineStr">
         <is>
-          <t>Nu</t>
+          <t>1X</t>
         </is>
       </c>
       <c r="F36" s="26" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="G36" s="26" t="inlineStr">
         <is>
-          <t>gg</t>
+          <t>dc</t>
         </is>
       </c>
     </row>
@@ -35168,22 +35168,22 @@
       </c>
       <c r="D39" s="25" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Double Chance X2</t>
         </is>
       </c>
       <c r="E39" s="24" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>X2</t>
         </is>
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="G39" s="24" t="inlineStr">
         <is>
-          <t>goals_ou</t>
+          <t>dc</t>
         </is>
       </c>
     </row>
@@ -35205,22 +35205,22 @@
       </c>
       <c r="D40" s="27" t="inlineStr">
         <is>
-          <t>Fouls O/U 20.5</t>
+          <t>Goals O/U 3.5</t>
         </is>
       </c>
       <c r="E40" s="26" t="inlineStr">
         <is>
-          <t>Over 20.5</t>
+          <t>Under 3.5</t>
         </is>
       </c>
       <c r="F40" s="26" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="G40" s="26" t="inlineStr">
         <is>
-          <t>fouls</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -35242,22 +35242,22 @@
       </c>
       <c r="D41" s="29" t="inlineStr">
         <is>
-          <t>Scorer Memphis Depay (Netherla)</t>
+          <t>Fouls O/U 20.5</t>
         </is>
       </c>
       <c r="E41" s="28" t="inlineStr">
         <is>
-          <t>To Score</t>
+          <t>Over 20.5</t>
         </is>
       </c>
       <c r="F41" s="28" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="G41" s="28" t="inlineStr">
         <is>
-          <t>scorers</t>
+          <t>fouls</t>
         </is>
       </c>
     </row>
@@ -35279,22 +35279,22 @@
       </c>
       <c r="D43" s="25" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Double Chance 1X</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>1X</t>
         </is>
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="G43" s="24" t="inlineStr">
         <is>
-          <t>goals_ou</t>
+          <t>dc</t>
         </is>
       </c>
     </row>
@@ -35316,22 +35316,22 @@
       </c>
       <c r="D44" s="27" t="inlineStr">
         <is>
-          <t>Yellow Cards O/U 4.5</t>
+          <t>Goals O/U 1.5</t>
         </is>
       </c>
       <c r="E44" s="26" t="inlineStr">
         <is>
-          <t>Under 4.5</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="F44" s="26" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="G44" s="26" t="inlineStr">
         <is>
-          <t>yellows</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -35353,22 +35353,22 @@
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>Fouls O/U 24.5</t>
+          <t>Yellow Cards O/U 4.5</t>
         </is>
       </c>
       <c r="E45" s="28" t="inlineStr">
         <is>
-          <t>Under 24.5</t>
+          <t>Under 4.5</t>
         </is>
       </c>
       <c r="F45" s="28" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="G45" s="28" t="inlineStr">
         <is>
-          <t>fouls</t>
+          <t>yellows</t>
         </is>
       </c>
     </row>
@@ -35427,22 +35427,22 @@
       </c>
       <c r="D48" s="27" t="inlineStr">
         <is>
-          <t>Fouls O/U 20.5</t>
+          <t>Goals O/U 1.5</t>
         </is>
       </c>
       <c r="E48" s="26" t="inlineStr">
         <is>
-          <t>Over 20.5</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="F48" s="26" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="G48" s="26" t="inlineStr">
         <is>
-          <t>fouls</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -35464,22 +35464,22 @@
       </c>
       <c r="D49" s="29" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Fouls O/U 20.5</t>
         </is>
       </c>
       <c r="E49" s="28" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Over 20.5</t>
         </is>
       </c>
       <c r="F49" s="28" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="G49" s="28" t="inlineStr">
         <is>
-          <t>goals_ou</t>
+          <t>fouls</t>
         </is>
       </c>
     </row>
@@ -35501,22 +35501,22 @@
       </c>
       <c r="D51" s="25" t="inlineStr">
         <is>
-          <t>GG (Both Teams Score)</t>
+          <t>Goals O/U 3.5</t>
         </is>
       </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>Nu</t>
+          <t>Under 3.5</t>
         </is>
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>gg</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -35538,22 +35538,22 @@
       </c>
       <c r="D52" s="27" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Draw No Bet Spain</t>
         </is>
       </c>
       <c r="E52" s="26" t="inlineStr">
         <is>
-          <t>1 (Spain)</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="F52" s="26" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="G52" s="26" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>dnb</t>
         </is>
       </c>
     </row>
@@ -35649,17 +35649,17 @@
       </c>
       <c r="D56" s="27" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Goals O/U 3.5</t>
         </is>
       </c>
       <c r="E56" s="26" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Under 3.5</t>
         </is>
       </c>
       <c r="F56" s="26" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="G56" s="26" t="inlineStr">
@@ -35723,17 +35723,17 @@
       </c>
       <c r="D59" s="25" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Goals O/U 3.5</t>
         </is>
       </c>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Under 3.5</t>
         </is>
       </c>
       <c r="F59" s="24" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="G59" s="24" t="inlineStr">
@@ -35871,17 +35871,17 @@
       </c>
       <c r="D64" s="27" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Goals O/U 1.5</t>
         </is>
       </c>
       <c r="E64" s="26" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="F64" s="26" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="G64" s="26" t="inlineStr">
@@ -35945,17 +35945,17 @@
       </c>
       <c r="D67" s="25" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Goals O/U 3.5</t>
         </is>
       </c>
       <c r="E67" s="24" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Under 3.5</t>
         </is>
       </c>
       <c r="F67" s="24" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="G67" s="24" t="inlineStr">
@@ -36056,22 +36056,22 @@
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Goals O/U 3.5</t>
         </is>
       </c>
       <c r="E71" s="24" t="inlineStr">
         <is>
-          <t>2 (Norway)</t>
+          <t>Under 3.5</t>
         </is>
       </c>
       <c r="F71" s="24" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="G71" s="24" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -36093,22 +36093,22 @@
       </c>
       <c r="D72" s="27" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Double Chance X2</t>
         </is>
       </c>
       <c r="E72" s="26" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>X2</t>
         </is>
       </c>
       <c r="F72" s="26" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="G72" s="26" t="inlineStr">
         <is>
-          <t>goals_ou</t>
+          <t>dc</t>
         </is>
       </c>
     </row>
@@ -36167,22 +36167,22 @@
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Goals O/U 2.5</t>
         </is>
       </c>
       <c r="E75" s="24" t="inlineStr">
         <is>
-          <t>1 (Argentina)</t>
+          <t>Under 2.5</t>
         </is>
       </c>
       <c r="F75" s="24" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="G75" s="24" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -36204,22 +36204,22 @@
       </c>
       <c r="D76" s="27" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>1X2 Result</t>
         </is>
       </c>
       <c r="E76" s="26" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>1 (Argentina)</t>
         </is>
       </c>
       <c r="F76" s="26" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="G76" s="26" t="inlineStr">
         <is>
-          <t>goals_ou</t>
+          <t>result</t>
         </is>
       </c>
     </row>
@@ -36278,22 +36278,22 @@
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Double Chance X2</t>
         </is>
       </c>
       <c r="E79" s="24" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>X2</t>
         </is>
       </c>
       <c r="F79" s="24" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="G79" s="24" t="inlineStr">
         <is>
-          <t>goals_ou</t>
+          <t>dc</t>
         </is>
       </c>
     </row>
@@ -36315,22 +36315,22 @@
       </c>
       <c r="D80" s="27" t="inlineStr">
         <is>
-          <t>Double Chance 1X</t>
+          <t>Goals O/U 3.5</t>
         </is>
       </c>
       <c r="E80" s="26" t="inlineStr">
         <is>
-          <t>1X</t>
+          <t>Under 3.5</t>
         </is>
       </c>
       <c r="F80" s="26" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="G80" s="26" t="inlineStr">
         <is>
-          <t>dc</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -36389,22 +36389,22 @@
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>GG (Both Teams Score)</t>
+          <t>Draw No Bet Portugal</t>
         </is>
       </c>
       <c r="E83" s="24" t="inlineStr">
         <is>
-          <t>Nu</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="F83" s="24" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="G83" s="24" t="inlineStr">
         <is>
-          <t>gg</t>
+          <t>dnb</t>
         </is>
       </c>
     </row>
@@ -36426,22 +36426,22 @@
       </c>
       <c r="D84" s="27" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Goals O/U 1.5</t>
         </is>
       </c>
       <c r="E84" s="26" t="inlineStr">
         <is>
-          <t>1 (Portugal)</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="F84" s="26" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="G84" s="26" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -36500,22 +36500,22 @@
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Draw No Bet England</t>
         </is>
       </c>
       <c r="E87" s="24" t="inlineStr">
         <is>
-          <t>1 (England)</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="F87" s="24" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="G87" s="24" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>dnb</t>
         </is>
       </c>
     </row>
@@ -36537,17 +36537,17 @@
       </c>
       <c r="D88" s="27" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Goals O/U 1.5</t>
         </is>
       </c>
       <c r="E88" s="26" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="F88" s="26" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="G88" s="26" t="inlineStr">
@@ -36611,22 +36611,22 @@
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Double Chance X2</t>
         </is>
       </c>
       <c r="E91" s="24" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>X2</t>
         </is>
       </c>
       <c r="F91" s="24" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>83.6%</t>
         </is>
       </c>
       <c r="G91" s="24" t="inlineStr">
         <is>
-          <t>goals_ou</t>
+          <t>dc</t>
         </is>
       </c>
     </row>
@@ -36648,22 +36648,22 @@
       </c>
       <c r="D92" s="27" t="inlineStr">
         <is>
-          <t>Double Chance X2</t>
+          <t>Goals O/U 1.5</t>
         </is>
       </c>
       <c r="E92" s="26" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="F92" s="26" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="G92" s="26" t="inlineStr">
         <is>
-          <t>dc</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -36722,17 +36722,17 @@
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>Goals O/U 0.5</t>
+          <t>Goals O/U 3.5</t>
         </is>
       </c>
       <c r="E95" s="24" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Under 3.5</t>
         </is>
       </c>
       <c r="F95" s="24" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="G95" s="24" t="inlineStr">
@@ -36977,22 +36977,22 @@
       </c>
       <c r="D5" s="30" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Goals O/U 2.5</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>1 (Canada)</t>
-        </is>
-      </c>
-      <c r="F5" s="26" t="inlineStr">
-        <is>
-          <t>60.8%</t>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -37199,22 +37199,22 @@
       </c>
       <c r="D11" s="30" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Goals O/U 2.5</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1 (Germany)</t>
-        </is>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t>85.0%</t>
+          <t>Under 2.5</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -37347,22 +37347,22 @@
       </c>
       <c r="D15" s="30" t="inlineStr">
         <is>
-          <t>GG (Both Teams Score)</t>
+          <t>Goals O/U 3.5</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Nu</t>
+          <t>Under 3.5</t>
         </is>
       </c>
       <c r="F15" s="26" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>gg</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -37421,22 +37421,22 @@
       </c>
       <c r="D17" s="30" t="inlineStr">
         <is>
-          <t>GG (Both Teams Score)</t>
+          <t>Double Chance 1X</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Da</t>
+          <t>1X</t>
         </is>
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>gg</t>
+          <t>dc</t>
         </is>
       </c>
     </row>
@@ -37495,22 +37495,22 @@
       </c>
       <c r="D19" s="30" t="inlineStr">
         <is>
-          <t>GG (Both Teams Score)</t>
+          <t>Double Chance X2</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Da</t>
+          <t>X2</t>
         </is>
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>gg</t>
+          <t>dc</t>
         </is>
       </c>
     </row>
@@ -37532,22 +37532,22 @@
       </c>
       <c r="D20" s="31" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Double Chance 1X</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>2 (Norway)</t>
-        </is>
-      </c>
-      <c r="F20" s="26" t="inlineStr">
-        <is>
-          <t>71.5%</t>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>dc</t>
         </is>
       </c>
     </row>
@@ -37569,22 +37569,22 @@
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Goals O/U 2.5</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>1 (Argentina)</t>
-        </is>
-      </c>
-      <c r="F21" s="26" t="inlineStr">
-        <is>
-          <t>71.4%</t>
+          <t>Under 2.5</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
+        <is>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>goals_ou</t>
         </is>
       </c>
     </row>
@@ -37606,22 +37606,22 @@
       </c>
       <c r="D22" s="31" t="inlineStr">
         <is>
-          <t>GG (Both Teams Score)</t>
+          <t>Draw No Bet Jordan</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="F22" s="28" t="inlineStr">
-        <is>
-          <t>51.0%</t>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="F22" s="32" t="inlineStr">
+        <is>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>gg</t>
+          <t>dnb</t>
         </is>
       </c>
     </row>
@@ -37643,22 +37643,22 @@
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
-          <t>GG (Both Teams Score)</t>
+          <t>Draw No Bet Portugal</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="F23" s="28" t="inlineStr">
-        <is>
-          <t>55.2%</t>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>gg</t>
+          <t>dnb</t>
         </is>
       </c>
     </row>
@@ -37680,22 +37680,22 @@
       </c>
       <c r="D24" s="31" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Draw No Bet England</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>1 (England)</t>
-        </is>
-      </c>
-      <c r="F24" s="26" t="inlineStr">
-        <is>
-          <t>62.8%</t>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>dnb</t>
         </is>
       </c>
     </row>
@@ -37754,22 +37754,22 @@
       </c>
       <c r="D26" s="31" t="inlineStr">
         <is>
-          <t>GG (Both Teams Score)</t>
+          <t>Double Chance 1X</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Nu</t>
+          <t>1X</t>
         </is>
       </c>
       <c r="F26" s="28" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>gg</t>
+          <t>dc</t>
         </is>
       </c>
     </row>

--- a/backtest_v3.xlsx
+++ b/backtest_v3.xlsx
@@ -6960,7 +6960,7 @@
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
@@ -13396,7 +13396,7 @@
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="E309" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F309" s="3" t="inlineStr">
@@ -14328,7 +14328,7 @@
       </c>
       <c r="E310" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="F310" s="5" t="inlineStr">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="E311" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="F311" s="3" t="inlineStr">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="E312" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="F312" s="5" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="E313" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F313" s="3" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="E316" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="F316" s="5" t="inlineStr">
@@ -14794,37 +14794,37 @@
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
-      <c r="A325" s="22" t="inlineStr">
+      <c r="A325" s="17" t="inlineStr">
         <is>
           <t>Netherlands vs Japan</t>
         </is>
       </c>
-      <c r="B325" s="22" t="inlineStr">
-        <is>
-          <t>Double Chance X2 *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C325" s="23" t="inlineStr">
+      <c r="B325" s="17" t="inlineStr">
+        <is>
+          <t>Double Chance X2</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
         <is>
           <t>X2</t>
         </is>
       </c>
-      <c r="D325" s="23" t="inlineStr">
+      <c r="D325" s="15" t="inlineStr">
         <is>
           <t>74.1%</t>
         </is>
       </c>
-      <c r="E325" s="23" t="inlineStr">
+      <c r="E325" s="3" t="inlineStr">
         <is>
           <t>1.80</t>
         </is>
       </c>
-      <c r="F325" s="23" t="inlineStr">
+      <c r="F325" s="3" t="inlineStr">
         <is>
           <t>dc</t>
         </is>
       </c>
-      <c r="G325" s="23" t="inlineStr">
+      <c r="G325" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -15164,37 +15164,37 @@
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
-      <c r="A335" s="17" t="inlineStr">
+      <c r="A335" s="22" t="inlineStr">
         <is>
           <t>Netherlands vs Japan</t>
         </is>
       </c>
-      <c r="B335" s="17" t="inlineStr">
-        <is>
-          <t>Draw No Bet Japan</t>
-        </is>
-      </c>
-      <c r="C335" s="3" t="inlineStr">
+      <c r="B335" s="22" t="inlineStr">
+        <is>
+          <t>Draw No Bet Japan *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C335" s="23" t="inlineStr">
         <is>
           <t>Win</t>
         </is>
       </c>
-      <c r="D335" s="11" t="inlineStr">
+      <c r="D335" s="23" t="inlineStr">
         <is>
           <t>57.3%</t>
         </is>
       </c>
-      <c r="E335" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F335" s="3" t="inlineStr">
+      <c r="E335" s="23" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="F335" s="23" t="inlineStr">
         <is>
           <t>dnb</t>
         </is>
       </c>
-      <c r="G335" s="3" t="inlineStr">
+      <c r="G335" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -15408,7 +15408,7 @@
       </c>
       <c r="E341" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F341" s="3" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="E349" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F349" s="3" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="E350" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F350" s="5" t="inlineStr">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="E351" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F351" s="3" t="inlineStr">
@@ -15815,7 +15815,7 @@
       </c>
       <c r="E352" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="F352" s="5" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="E353" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F353" s="3" t="inlineStr">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="E354" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="F354" s="5" t="inlineStr">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="E355" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="F355" s="3" t="inlineStr">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="E356" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="F356" s="5" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="E374" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="F374" s="5" t="inlineStr">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="E379" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F379" s="3" t="inlineStr">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="E384" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="F384" s="5" t="inlineStr">
@@ -16969,7 +16969,7 @@
       </c>
       <c r="E385" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F385" s="3" t="inlineStr">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="E386" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="F386" s="5" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="E387" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="F387" s="3" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="E388" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="F388" s="5" t="inlineStr">
@@ -17117,7 +17117,7 @@
       </c>
       <c r="E389" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="F389" s="3" t="inlineStr">
@@ -17154,7 +17154,7 @@
       </c>
       <c r="E390" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="F390" s="5" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="E391" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F391" s="3" t="inlineStr">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="E399" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F399" s="3" t="inlineStr">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="E416" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="F416" s="5" t="inlineStr">
@@ -18160,7 +18160,7 @@
       </c>
       <c r="E419" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F419" s="3" t="inlineStr">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="E420" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F420" s="5" t="inlineStr">
@@ -18234,7 +18234,7 @@
       </c>
       <c r="E421" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F421" s="3" t="inlineStr">
@@ -18271,7 +18271,7 @@
       </c>
       <c r="E422" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F422" s="5" t="inlineStr">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="E423" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="F423" s="3" t="inlineStr">
@@ -18345,7 +18345,7 @@
       </c>
       <c r="E424" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="F424" s="5" t="inlineStr">
@@ -18382,7 +18382,7 @@
       </c>
       <c r="E425" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="F425" s="3" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="E426" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="F426" s="5" t="inlineStr">
@@ -18500,7 +18500,7 @@
       </c>
       <c r="E430" s="23" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="F430" s="23" t="inlineStr">
@@ -19351,7 +19351,7 @@
       </c>
       <c r="E453" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F453" s="3" t="inlineStr">
@@ -19388,7 +19388,7 @@
       </c>
       <c r="E454" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="F454" s="5" t="inlineStr">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="E455" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="F455" s="3" t="inlineStr">
@@ -19462,7 +19462,7 @@
       </c>
       <c r="E456" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="F456" s="5" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="E457" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="F457" s="3" t="inlineStr">
@@ -19536,7 +19536,7 @@
       </c>
       <c r="E458" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="F458" s="5" t="inlineStr">
@@ -19573,7 +19573,7 @@
       </c>
       <c r="E459" s="3" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="F459" s="3" t="inlineStr">
@@ -19610,7 +19610,7 @@
       </c>
       <c r="E460" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="F460" s="5" t="inlineStr">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="E461" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F461" s="3" t="inlineStr">
@@ -20690,7 +20690,7 @@
       </c>
       <c r="E491" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F491" s="3" t="inlineStr">
@@ -20727,7 +20727,7 @@
       </c>
       <c r="E492" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F492" s="5" t="inlineStr">
@@ -20764,7 +20764,7 @@
       </c>
       <c r="E493" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F493" s="3" t="inlineStr">
@@ -20838,7 +20838,7 @@
       </c>
       <c r="E495" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F495" s="3" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="E496" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F496" s="5" t="inlineStr">
@@ -20949,7 +20949,7 @@
       </c>
       <c r="E498" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="F498" s="5" t="inlineStr">
@@ -20986,7 +20986,7 @@
       </c>
       <c r="E499" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="F499" s="3" t="inlineStr">
@@ -21023,7 +21023,7 @@
       </c>
       <c r="E500" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="F500" s="5" t="inlineStr">
@@ -22103,7 +22103,7 @@
       </c>
       <c r="E531" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F531" s="3" t="inlineStr">
@@ -22140,7 +22140,7 @@
       </c>
       <c r="E532" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="F532" s="5" t="inlineStr">
@@ -22177,7 +22177,7 @@
       </c>
       <c r="E533" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="F533" s="3" t="inlineStr">
@@ -22214,7 +22214,7 @@
       </c>
       <c r="E534" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F534" s="5" t="inlineStr">
@@ -22251,7 +22251,7 @@
       </c>
       <c r="E535" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F535" s="3" t="inlineStr">
@@ -22288,7 +22288,7 @@
       </c>
       <c r="E536" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="F536" s="5" t="inlineStr">
@@ -22325,7 +22325,7 @@
       </c>
       <c r="E537" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="F537" s="3" t="inlineStr">
@@ -22362,7 +22362,7 @@
       </c>
       <c r="E538" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="F538" s="5" t="inlineStr">
@@ -23479,7 +23479,7 @@
       </c>
       <c r="E570" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="F570" s="5" t="inlineStr">
@@ -23516,7 +23516,7 @@
       </c>
       <c r="E571" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="F571" s="3" t="inlineStr">
@@ -23553,7 +23553,7 @@
       </c>
       <c r="E572" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="F572" s="5" t="inlineStr">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="E573" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F573" s="3" t="inlineStr">
@@ -23627,7 +23627,7 @@
       </c>
       <c r="E574" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F574" s="5" t="inlineStr">
@@ -23664,7 +23664,7 @@
       </c>
       <c r="E575" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F575" s="3" t="inlineStr">
@@ -23701,7 +23701,7 @@
       </c>
       <c r="E576" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="F576" s="5" t="inlineStr">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="E577" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="F577" s="3" t="inlineStr">
@@ -23967,7 +23967,7 @@
       </c>
       <c r="E585" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F585" s="3" t="inlineStr">
@@ -24670,7 +24670,7 @@
       </c>
       <c r="E604" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="F604" s="5" t="inlineStr">
@@ -24707,7 +24707,7 @@
       </c>
       <c r="E605" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="F605" s="3" t="inlineStr">
@@ -24781,7 +24781,7 @@
       </c>
       <c r="E607" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F607" s="3" t="inlineStr">
@@ -24818,7 +24818,7 @@
       </c>
       <c r="E608" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F608" s="5" t="inlineStr">
@@ -24855,7 +24855,7 @@
       </c>
       <c r="E609" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F609" s="3" t="inlineStr">
@@ -24892,7 +24892,7 @@
       </c>
       <c r="E610" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F610" s="5" t="inlineStr">
@@ -24929,7 +24929,7 @@
       </c>
       <c r="E611" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="F611" s="3" t="inlineStr">
@@ -24966,7 +24966,7 @@
       </c>
       <c r="E612" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="F612" s="5" t="inlineStr">
@@ -25003,7 +25003,7 @@
       </c>
       <c r="E613" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F613" s="3" t="inlineStr">
@@ -25972,7 +25972,7 @@
       </c>
       <c r="E641" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F641" s="3" t="inlineStr">
@@ -26009,7 +26009,7 @@
       </c>
       <c r="E642" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="F642" s="5" t="inlineStr">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="E643" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="F643" s="3" t="inlineStr">
@@ -26120,7 +26120,7 @@
       </c>
       <c r="E645" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="F645" s="3" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="E647" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="F647" s="3" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="E648" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F648" s="5" t="inlineStr">
@@ -26268,7 +26268,7 @@
       </c>
       <c r="E649" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="F649" s="3" t="inlineStr">
@@ -26305,7 +26305,7 @@
       </c>
       <c r="E650" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="F650" s="5" t="inlineStr">
@@ -26423,7 +26423,7 @@
       </c>
       <c r="E655" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F655" s="3" t="inlineStr">
@@ -27311,7 +27311,7 @@
       </c>
       <c r="E679" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="F679" s="3" t="inlineStr">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="E680" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="F680" s="5" t="inlineStr">
@@ -27385,7 +27385,7 @@
       </c>
       <c r="E681" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="F681" s="3" t="inlineStr">
@@ -27422,7 +27422,7 @@
       </c>
       <c r="E682" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="F682" s="5" t="inlineStr">
@@ -27496,7 +27496,7 @@
       </c>
       <c r="E684" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F684" s="5" t="inlineStr">
@@ -27533,7 +27533,7 @@
       </c>
       <c r="E685" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="F685" s="3" t="inlineStr">
@@ -27570,7 +27570,7 @@
       </c>
       <c r="E686" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F686" s="5" t="inlineStr">
@@ -27607,7 +27607,7 @@
       </c>
       <c r="E687" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="F687" s="3" t="inlineStr">
@@ -27644,7 +27644,7 @@
       </c>
       <c r="E688" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="F688" s="5" t="inlineStr">
@@ -28687,7 +28687,7 @@
       </c>
       <c r="E718" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F718" s="5" t="inlineStr">
@@ -28761,7 +28761,7 @@
       </c>
       <c r="E720" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F720" s="5" t="inlineStr">
@@ -28798,7 +28798,7 @@
       </c>
       <c r="E721" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="F721" s="3" t="inlineStr">
@@ -28835,7 +28835,7 @@
       </c>
       <c r="E722" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F722" s="5" t="inlineStr">
@@ -28872,7 +28872,7 @@
       </c>
       <c r="E723" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="F723" s="3" t="inlineStr">
@@ -28909,7 +28909,7 @@
       </c>
       <c r="E724" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="F724" s="5" t="inlineStr">
@@ -28946,7 +28946,7 @@
       </c>
       <c r="E725" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="F725" s="3" t="inlineStr">
@@ -28983,7 +28983,7 @@
       </c>
       <c r="E726" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F726" s="5" t="inlineStr">
@@ -29005,37 +29005,37 @@
       </c>
     </row>
     <row r="729" ht="15" customHeight="1">
-      <c r="A729" s="17" t="inlineStr">
+      <c r="A729" s="22" t="inlineStr">
         <is>
           <t>Portugal vs DR Congo</t>
         </is>
       </c>
-      <c r="B729" s="17" t="inlineStr">
-        <is>
-          <t>Double Chance 1X</t>
-        </is>
-      </c>
-      <c r="C729" s="3" t="inlineStr">
+      <c r="B729" s="22" t="inlineStr">
+        <is>
+          <t>Double Chance 1X *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C729" s="23" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="D729" s="4" t="inlineStr">
+      <c r="D729" s="23" t="inlineStr">
         <is>
           <t>92.4%</t>
         </is>
       </c>
-      <c r="E729" s="3" t="inlineStr">
+      <c r="E729" s="23" t="inlineStr">
         <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="F729" s="3" t="inlineStr">
+      <c r="F729" s="23" t="inlineStr">
         <is>
           <t>dc</t>
         </is>
       </c>
-      <c r="G729" s="3" t="inlineStr">
+      <c r="G729" s="23" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -29079,37 +29079,37 @@
       </c>
     </row>
     <row r="731" ht="15" customHeight="1">
-      <c r="A731" s="22" t="inlineStr">
+      <c r="A731" s="17" t="inlineStr">
         <is>
           <t>Portugal vs DR Congo</t>
         </is>
       </c>
-      <c r="B731" s="22" t="inlineStr">
-        <is>
-          <t>Draw No Bet Portugal *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C731" s="23" t="inlineStr">
+      <c r="B731" s="17" t="inlineStr">
+        <is>
+          <t>Draw No Bet Portugal</t>
+        </is>
+      </c>
+      <c r="C731" s="3" t="inlineStr">
         <is>
           <t>Win</t>
         </is>
       </c>
-      <c r="D731" s="23" t="inlineStr">
+      <c r="D731" s="4" t="inlineStr">
         <is>
           <t>90.0%</t>
         </is>
       </c>
-      <c r="E731" s="23" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="F731" s="23" t="inlineStr">
+      <c r="E731" s="3" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="F731" s="3" t="inlineStr">
         <is>
           <t>dnb</t>
         </is>
       </c>
-      <c r="G731" s="23" t="inlineStr">
+      <c r="G731" s="3" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -29915,7 +29915,7 @@
       </c>
       <c r="E753" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="F753" s="3" t="inlineStr">
@@ -29952,7 +29952,7 @@
       </c>
       <c r="E754" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F754" s="5" t="inlineStr">
@@ -29989,7 +29989,7 @@
       </c>
       <c r="E755" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F755" s="3" t="inlineStr">
@@ -30026,7 +30026,7 @@
       </c>
       <c r="E756" s="5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F756" s="5" t="inlineStr">
@@ -30063,7 +30063,7 @@
       </c>
       <c r="E757" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F757" s="3" t="inlineStr">
@@ -30100,7 +30100,7 @@
       </c>
       <c r="E758" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F758" s="5" t="inlineStr">
@@ -30137,7 +30137,7 @@
       </c>
       <c r="E759" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="F759" s="3" t="inlineStr">
@@ -30211,7 +30211,7 @@
       </c>
       <c r="E761" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="F761" s="3" t="inlineStr">
@@ -30248,7 +30248,7 @@
       </c>
       <c r="E762" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="F762" s="5" t="inlineStr">
@@ -30381,37 +30381,37 @@
       </c>
     </row>
     <row r="768" ht="15" customHeight="1">
-      <c r="A768" s="22" t="inlineStr">
+      <c r="A768" s="18" t="inlineStr">
         <is>
           <t>England vs Croatia</t>
         </is>
       </c>
-      <c r="B768" s="22" t="inlineStr">
-        <is>
-          <t>Draw No Bet England *** ACCUMULATOR</t>
-        </is>
-      </c>
-      <c r="C768" s="23" t="inlineStr">
+      <c r="B768" s="18" t="inlineStr">
+        <is>
+          <t>Draw No Bet England</t>
+        </is>
+      </c>
+      <c r="C768" s="5" t="inlineStr">
         <is>
           <t>Win</t>
         </is>
       </c>
-      <c r="D768" s="23" t="inlineStr">
+      <c r="D768" s="4" t="inlineStr">
         <is>
           <t>82.3%</t>
         </is>
       </c>
-      <c r="E768" s="23" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="F768" s="23" t="inlineStr">
+      <c r="E768" s="5" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="F768" s="5" t="inlineStr">
         <is>
           <t>dnb</t>
         </is>
       </c>
-      <c r="G768" s="23" t="inlineStr">
+      <c r="G768" s="5" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -30751,37 +30751,37 @@
       </c>
     </row>
     <row r="778" ht="15" customHeight="1">
-      <c r="A778" s="18" t="inlineStr">
+      <c r="A778" s="22" t="inlineStr">
         <is>
           <t>England vs Croatia</t>
         </is>
       </c>
-      <c r="B778" s="18" t="inlineStr">
-        <is>
-          <t>1X2 Result</t>
-        </is>
-      </c>
-      <c r="C778" s="5" t="inlineStr">
+      <c r="B778" s="22" t="inlineStr">
+        <is>
+          <t>1X2 Result *** ACCUMULATOR</t>
+        </is>
+      </c>
+      <c r="C778" s="23" t="inlineStr">
         <is>
           <t>1 (England)</t>
         </is>
       </c>
-      <c r="D778" s="15" t="inlineStr">
+      <c r="D778" s="23" t="inlineStr">
         <is>
           <t>62.8%</t>
         </is>
       </c>
-      <c r="E778" s="5" t="inlineStr">
+      <c r="E778" s="23" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="F778" s="5" t="inlineStr">
+      <c r="F778" s="23" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="G778" s="5" t="inlineStr">
+      <c r="G778" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -31180,7 +31180,7 @@
       </c>
       <c r="E789" s="3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F789" s="3" t="inlineStr">
@@ -31254,7 +31254,7 @@
       </c>
       <c r="E791" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="F791" s="3" t="inlineStr">
@@ -31291,7 +31291,7 @@
       </c>
       <c r="E792" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F792" s="5" t="inlineStr">
@@ -31328,7 +31328,7 @@
       </c>
       <c r="E793" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F793" s="3" t="inlineStr">
@@ -31365,7 +31365,7 @@
       </c>
       <c r="E794" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="F794" s="5" t="inlineStr">
@@ -31402,7 +31402,7 @@
       </c>
       <c r="E795" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F795" s="3" t="inlineStr">
@@ -31439,7 +31439,7 @@
       </c>
       <c r="E796" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="F796" s="5" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="E797" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="F797" s="3" t="inlineStr">
@@ -31513,7 +31513,7 @@
       </c>
       <c r="E798" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="F798" s="5" t="inlineStr">
@@ -32482,7 +32482,7 @@
       </c>
       <c r="E826" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="F826" s="5" t="inlineStr">
@@ -32519,7 +32519,7 @@
       </c>
       <c r="E827" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F827" s="3" t="inlineStr">
@@ -32556,7 +32556,7 @@
       </c>
       <c r="E828" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="F828" s="5" t="inlineStr">
@@ -32593,7 +32593,7 @@
       </c>
       <c r="E829" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="F829" s="3" t="inlineStr">
@@ -32630,7 +32630,7 @@
       </c>
       <c r="E830" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="F830" s="5" t="inlineStr">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="E831" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F831" s="3" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="E832" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="F832" s="5" t="inlineStr">
@@ -32741,7 +32741,7 @@
       </c>
       <c r="E833" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F833" s="3" t="inlineStr">
@@ -33747,7 +33747,7 @@
       </c>
       <c r="E862" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F862" s="5" t="inlineStr">
@@ -33784,7 +33784,7 @@
       </c>
       <c r="E863" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F863" s="3" t="inlineStr">
@@ -33858,7 +33858,7 @@
       </c>
       <c r="E865" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F865" s="3" t="inlineStr">
@@ -33895,7 +33895,7 @@
       </c>
       <c r="E866" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="F866" s="5" t="inlineStr">
@@ -33932,7 +33932,7 @@
       </c>
       <c r="E867" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F867" s="3" t="inlineStr">
@@ -33969,7 +33969,7 @@
       </c>
       <c r="E868" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="F868" s="5" t="inlineStr">
@@ -34006,7 +34006,7 @@
       </c>
       <c r="E869" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="F869" s="3" t="inlineStr">
@@ -34043,7 +34043,7 @@
       </c>
       <c r="E870" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F870" s="5" t="inlineStr">
@@ -35168,22 +35168,22 @@
       </c>
       <c r="D39" s="25" t="inlineStr">
         <is>
-          <t>Double Chance X2</t>
+          <t>Draw No Bet Japan</t>
         </is>
       </c>
       <c r="E39" s="24" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="G39" s="24" t="inlineStr">
         <is>
-          <t>dc</t>
+          <t>dnb</t>
         </is>
       </c>
     </row>
@@ -36389,22 +36389,22 @@
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>Draw No Bet Portugal</t>
+          <t>Double Chance 1X</t>
         </is>
       </c>
       <c r="E83" s="24" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>1X</t>
         </is>
       </c>
       <c r="F83" s="24" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="G83" s="24" t="inlineStr">
         <is>
-          <t>dnb</t>
+          <t>dc</t>
         </is>
       </c>
     </row>
@@ -36500,22 +36500,22 @@
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>Draw No Bet England</t>
+          <t>1X2 Result</t>
         </is>
       </c>
       <c r="E87" s="24" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>1 (England)</t>
         </is>
       </c>
       <c r="F87" s="24" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G87" s="24" t="inlineStr">
         <is>
-          <t>dnb</t>
+          <t>result</t>
         </is>
       </c>
     </row>
@@ -37125,22 +37125,22 @@
       </c>
       <c r="D9" s="30" t="inlineStr">
         <is>
-          <t>GG (Both Teams Score)</t>
+          <t>Correct Score 2-1</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="F9" s="28" t="inlineStr">
-        <is>
-          <t>52.7%</t>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F9" s="32" t="inlineStr">
+        <is>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>gg</t>
+          <t>correct</t>
         </is>
       </c>
     </row>
@@ -37162,22 +37162,22 @@
       </c>
       <c r="D10" s="31" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Correct Score 2-1</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>2 (Turkey)</t>
-        </is>
-      </c>
-      <c r="F10" s="26" t="inlineStr">
-        <is>
-          <t>64.0%</t>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>correct</t>
         </is>
       </c>
     </row>
@@ -37199,22 +37199,22 @@
       </c>
       <c r="D11" s="30" t="inlineStr">
         <is>
-          <t>Goals O/U 2.5</t>
+          <t>Correct Score 1-1</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Under 2.5</t>
-        </is>
-      </c>
-      <c r="F11" s="28" t="inlineStr">
-        <is>
-          <t>50.6%</t>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>goals_ou</t>
+          <t>correct</t>
         </is>
       </c>
     </row>
@@ -37236,22 +37236,22 @@
       </c>
       <c r="D12" s="31" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Draw No Bet Japan</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>X (egal)</t>
-        </is>
-      </c>
-      <c r="F12" s="32" t="inlineStr">
-        <is>
-          <t>39.2%</t>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>dnb</t>
         </is>
       </c>
     </row>
@@ -37310,22 +37310,22 @@
       </c>
       <c r="D14" s="31" t="inlineStr">
         <is>
-          <t>1X2 Result</t>
+          <t>Correct Score 0-2</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>1 (Sweden)</t>
-        </is>
-      </c>
-      <c r="F14" s="26" t="inlineStr">
-        <is>
-          <t>61.6%</t>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>correct</t>
         </is>
       </c>
     </row>
@@ -37347,22 +37347,22 @@
       </c>
       <c r="D15" s="30" t="inlineStr">
         <is>
-          <t>Goals O/U 3.5</t>
+          <t>Correct Score 1-1</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Under 3.5</t>
-        </is>
-      </c>
-      <c r="F15" s="26" t="inlineStr">
-        <is>
-          <t>72.8%</t>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>goals_ou</t>
+          <t>correct</t>
         </is>
       </c>
     </row>
@@ -37421,22 +37421,22 @@
       </c>
       <c r="D17" s="30" t="inlineStr">
         <is>
-          <t>Double Chance 1X</t>
+          <t>Correct Score 2-1</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>1X</t>
-        </is>
-      </c>
-      <c r="F17" s="28" t="inlineStr">
-        <is>
-          <t>46.8%</t>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>dc</t>
+          <t>correct</t>
         </is>
       </c>
     </row>
@@ -37569,22 +37569,22 @@
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
-          <t>Goals O/U 2.5</t>
+          <t>Correct Score 0-1</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Under 2.5</t>
-        </is>
-      </c>
-      <c r="F21" s="28" t="inlineStr">
-        <is>
-          <t>55.2%</t>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>goals_ou</t>
+          <t>correct</t>
         </is>
       </c>
     </row>
@@ -37606,22 +37606,22 @@
       </c>
       <c r="D22" s="31" t="inlineStr">
         <is>
-          <t>Draw No Bet Jordan</t>
+          <t>Correct Score 0-1</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="F22" s="32" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>dnb</t>
+          <t>correct</t>
         </is>
       </c>
     </row>
@@ -37643,22 +37643,22 @@
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
-          <t>Draw No Bet Portugal</t>
+          <t>Correct Score 1-1</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="F23" s="24" t="inlineStr">
-        <is>
-          <t>90.0%</t>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="F23" s="32" t="inlineStr">
+        <is>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>dnb</t>
+          <t>correct</t>
         </is>
       </c>
     </row>
@@ -37680,22 +37680,22 @@
       </c>
       <c r="D24" s="31" t="inlineStr">
         <is>
-          <t>Draw No Bet England</t>
+          <t>Correct Score 1-2</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="F24" s="24" t="inlineStr">
-        <is>
-          <t>82.3%</t>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="F24" s="32" t="inlineStr">
+        <is>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>dnb</t>
+          <t>correct</t>
         </is>
       </c>
     </row>
